--- a/mortality_odds_only_pdl1.xlsx
+++ b/mortality_odds_only_pdl1.xlsx
@@ -14472,22 +14472,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="25">
-        <v>1.3784810000000001</v>
+        <v>1.2863150000000001</v>
       </c>
       <c r="C2" s="26">
-        <v>0.45717659999999999</v>
+        <v>0.44059510000000002</v>
       </c>
       <c r="D2" s="27">
-        <v>0.96999999999999997</v>
+        <v>0.73999999999999999</v>
       </c>
       <c r="E2" s="28">
-        <v>0.33300000000000002</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="F2" s="29">
-        <v>0.71961109999999995</v>
+        <v>0.65733900000000001</v>
       </c>
       <c r="G2" s="30">
-        <v>2.6406079999999999</v>
+        <v>2.5171269999999999</v>
       </c>
     </row>
     <row r="3">
@@ -14495,22 +14495,22 @@
         <v>8</v>
       </c>
       <c r="B3" s="33">
-        <v>0.97305660000000005</v>
+        <v>0.88405290000000003</v>
       </c>
       <c r="C3" s="34">
-        <v>0.31598219999999999</v>
+        <v>0.29626010000000003</v>
       </c>
       <c r="D3" s="35">
-        <v>-0.080000000000000002</v>
+        <v>-0.37</v>
       </c>
       <c r="E3" s="36">
-        <v>0.93300000000000005</v>
+        <v>0.71299999999999997</v>
       </c>
       <c r="F3" s="37">
-        <v>0.51490380000000002</v>
+        <v>0.4583816</v>
       </c>
       <c r="G3" s="38">
-        <v>1.8388659999999999</v>
+        <v>1.7050190000000001</v>
       </c>
     </row>
     <row r="4">
@@ -14518,22 +14518,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="41">
-        <v>1.6322479999999999</v>
+        <v>1.581906</v>
       </c>
       <c r="C4" s="42">
-        <v>0.60336040000000002</v>
+        <v>0.60343970000000002</v>
       </c>
       <c r="D4" s="43">
-        <v>1.3300000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="E4" s="44">
-        <v>0.185</v>
+        <v>0.22900000000000001</v>
       </c>
       <c r="F4" s="45">
-        <v>0.79093309999999995</v>
+        <v>0.74899380000000004</v>
       </c>
       <c r="G4" s="46">
-        <v>3.368471</v>
+        <v>3.3410519999999999</v>
       </c>
     </row>
     <row r="5">
@@ -14541,22 +14541,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="49">
-        <v>1.009717</v>
+        <v>0.86022900000000002</v>
       </c>
       <c r="C5" s="50">
-        <v>0.31779259999999998</v>
+        <v>0.2801882</v>
       </c>
       <c r="D5" s="51">
-        <v>0.029999999999999999</v>
+        <v>-0.46000000000000002</v>
       </c>
       <c r="E5" s="52">
-        <v>0.97499999999999998</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="F5" s="53">
-        <v>0.54487560000000002</v>
+        <v>0.45432470000000003</v>
       </c>
       <c r="G5" s="54">
-        <v>1.871122</v>
+        <v>1.6287780000000001</v>
       </c>
     </row>
     <row r="6">
@@ -14564,22 +14564,22 @@
         <v>11</v>
       </c>
       <c r="B6" s="57">
-        <v>1.0011019999999999</v>
+        <v>0.91204249999999998</v>
       </c>
       <c r="C6" s="58">
-        <v>0.3265113</v>
+        <v>0.30697819999999998</v>
       </c>
       <c r="D6" s="59">
-        <v>0</v>
+        <v>-0.27000000000000002</v>
       </c>
       <c r="E6" s="60">
-        <v>0.997</v>
+        <v>0.78400000000000003</v>
       </c>
       <c r="F6" s="61">
-        <v>0.52827199999999996</v>
+        <v>0.47153610000000001</v>
       </c>
       <c r="G6" s="62">
-        <v>1.89714</v>
+        <v>1.7640670000000001</v>
       </c>
     </row>
     <row r="7">
@@ -14587,22 +14587,22 @@
         <v>12</v>
       </c>
       <c r="B7" s="65">
-        <v>0.85742689999999999</v>
+        <v>0.80380490000000004</v>
       </c>
       <c r="C7" s="66">
-        <v>0.48801319999999998</v>
+        <v>0.4619954</v>
       </c>
       <c r="D7" s="67">
-        <v>-0.27000000000000002</v>
+        <v>-0.38</v>
       </c>
       <c r="E7" s="68">
-        <v>0.78700000000000003</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="F7" s="69">
-        <v>0.28101340000000003</v>
+        <v>0.2605634</v>
       </c>
       <c r="G7" s="70">
-        <v>2.616177</v>
+        <v>2.479635</v>
       </c>
     </row>
     <row r="8">
@@ -14610,16 +14610,16 @@
         <v>13</v>
       </c>
       <c r="B8" s="73">
-        <v>3.1400000000000003e-08</v>
+        <v>2.6799999999999999e-08</v>
       </c>
       <c r="C8" s="74">
-        <v>0.0001727</v>
+        <v>0.0001626</v>
       </c>
       <c r="D8" s="75">
         <v>-0</v>
       </c>
       <c r="E8" s="76">
-        <v>0.997</v>
+        <v>0.998</v>
       </c>
       <c r="F8" s="77">
         <v>0</v>
@@ -14633,10 +14633,10 @@
         <v>15</v>
       </c>
       <c r="B9" s="81">
-        <v>2.2200000000000001e-49</v>
+        <v>1.4100000000000001e-49</v>
       </c>
       <c r="C9" s="82">
-        <v>8.9299999999999996e-46</v>
+        <v>5.66e-46</v>
       </c>
       <c r="D9" s="83">
         <v>-0.029999999999999999</v>
@@ -14656,22 +14656,22 @@
         <v>16</v>
       </c>
       <c r="B10" s="89">
-        <v>0.65959829999999997</v>
+        <v>0.5914644</v>
       </c>
       <c r="C10" s="90">
-        <v>0.43744529999999998</v>
+        <v>0.43251780000000001</v>
       </c>
       <c r="D10" s="91">
-        <v>-0.63</v>
+        <v>-0.71999999999999997</v>
       </c>
       <c r="E10" s="92">
-        <v>0.53000000000000003</v>
+        <v>0.47299999999999998</v>
       </c>
       <c r="F10" s="93">
-        <v>0.179789</v>
+        <v>0.14108270000000001</v>
       </c>
       <c r="G10" s="94">
-        <v>2.4198919999999999</v>
+        <v>2.4796100000000001</v>
       </c>
     </row>
     <row r="11">
@@ -14679,22 +14679,22 @@
         <v>17</v>
       </c>
       <c r="B11" s="97">
-        <v>2.4154629999999999</v>
+        <v>2.2221890000000002</v>
       </c>
       <c r="C11" s="98">
-        <v>2.5847340000000001</v>
+        <v>2.3883749999999999</v>
       </c>
       <c r="D11" s="99">
-        <v>0.81999999999999995</v>
+        <v>0.73999999999999999</v>
       </c>
       <c r="E11" s="100">
-        <v>0.40999999999999998</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="F11" s="101">
-        <v>0.29658440000000003</v>
+        <v>0.27034740000000002</v>
       </c>
       <c r="G11" s="102">
-        <v>19.672180000000001</v>
+        <v>18.265840000000001</v>
       </c>
     </row>
     <row r="12">
@@ -14748,22 +14748,22 @@
         <v>1</v>
       </c>
       <c r="B14" s="121">
-        <v>0.7364735</v>
+        <v>0.74421040000000005</v>
       </c>
       <c r="C14" s="122">
-        <v>0.19626009999999999</v>
+        <v>0.20542740000000001</v>
       </c>
       <c r="D14" s="123">
-        <v>-1.1499999999999999</v>
+        <v>-1.0700000000000001</v>
       </c>
       <c r="E14" s="124">
-        <v>0.251</v>
+        <v>0.28399999999999997</v>
       </c>
       <c r="F14" s="125">
-        <v>0.43684109999999998</v>
+        <v>0.43324649999999998</v>
       </c>
       <c r="G14" s="126">
-        <v>1.2416259999999999</v>
+        <v>1.2783690000000001</v>
       </c>
     </row>
     <row r="15">
@@ -14817,22 +14817,22 @@
         <v>1</v>
       </c>
       <c r="B17" s="145">
-        <v>0.675701</v>
+        <v>0.71880359999999999</v>
       </c>
       <c r="C17" s="146">
-        <v>0.42221009999999998</v>
+        <v>0.46103040000000001</v>
       </c>
       <c r="D17" s="147">
-        <v>-0.63</v>
+        <v>-0.51000000000000001</v>
       </c>
       <c r="E17" s="148">
-        <v>0.53000000000000003</v>
+        <v>0.60699999999999999</v>
       </c>
       <c r="F17" s="149">
-        <v>0.19855619999999999</v>
+        <v>0.2044851</v>
       </c>
       <c r="G17" s="150">
-        <v>2.2994590000000001</v>
+        <v>2.5267300000000001</v>
       </c>
     </row>
     <row r="18">
@@ -14886,22 +14886,22 @@
         <v>1</v>
       </c>
       <c r="B20" s="169">
-        <v>0.84958820000000002</v>
+        <v>0.85861869999999996</v>
       </c>
       <c r="C20" s="170">
-        <v>0.22635330000000001</v>
+        <v>0.2363934</v>
       </c>
       <c r="D20" s="171">
-        <v>-0.60999999999999999</v>
+        <v>-0.55000000000000005</v>
       </c>
       <c r="E20" s="172">
-        <v>0.54100000000000004</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="F20" s="173">
-        <v>0.50399400000000005</v>
+        <v>0.50055179999999999</v>
       </c>
       <c r="G20" s="174">
-        <v>1.4321600000000001</v>
+        <v>1.4728270000000001</v>
       </c>
     </row>
     <row r="21">
@@ -14955,22 +14955,22 @@
         <v>1</v>
       </c>
       <c r="B23" s="193">
-        <v>0.92583819999999995</v>
+        <v>0.9566789</v>
       </c>
       <c r="C23" s="194">
-        <v>0.24126110000000001</v>
+        <v>0.25803959999999998</v>
       </c>
       <c r="D23" s="195">
-        <v>-0.29999999999999999</v>
+        <v>-0.16</v>
       </c>
       <c r="E23" s="196">
-        <v>0.76700000000000002</v>
+        <v>0.87</v>
       </c>
       <c r="F23" s="197">
-        <v>0.5555502</v>
+        <v>0.5638666</v>
       </c>
       <c r="G23" s="198">
-        <v>1.542932</v>
+        <v>1.62314</v>
       </c>
     </row>
     <row r="24">
@@ -15024,22 +15024,22 @@
         <v>1</v>
       </c>
       <c r="B26" s="217">
-        <v>4.7898230000000002</v>
+        <v>4.866091</v>
       </c>
       <c r="C26" s="218">
-        <v>3.8024619999999998</v>
+        <v>3.8655529999999998</v>
       </c>
       <c r="D26" s="219">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="E26" s="220">
-        <v>0.048000000000000001</v>
+        <v>0.045999999999999999</v>
       </c>
       <c r="F26" s="221">
-        <v>1.010607</v>
+        <v>1.025647</v>
       </c>
       <c r="G26" s="222">
-        <v>22.701609999999999</v>
+        <v>23.086729999999999</v>
       </c>
     </row>
     <row r="27">
@@ -15093,22 +15093,22 @@
         <v>1</v>
       </c>
       <c r="B29" s="241">
-        <v>3.4060389999999998</v>
+        <v>3.8753489999999999</v>
       </c>
       <c r="C29" s="242">
-        <v>1.191155</v>
+        <v>1.387805</v>
       </c>
       <c r="D29" s="243">
-        <v>3.5</v>
+        <v>3.7799999999999998</v>
       </c>
       <c r="E29" s="244">
         <v>0</v>
       </c>
       <c r="F29" s="245">
-        <v>1.7162029999999999</v>
+        <v>1.9208179999999999</v>
       </c>
       <c r="G29" s="246">
-        <v>6.7597500000000004</v>
+        <v>7.8187150000000001</v>
       </c>
     </row>
     <row r="30">
@@ -15162,22 +15162,22 @@
         <v>1</v>
       </c>
       <c r="B32" s="265">
-        <v>2.705057</v>
+        <v>2.5677129999999999</v>
       </c>
       <c r="C32" s="266">
-        <v>1.7626740000000001</v>
+        <v>1.691543</v>
       </c>
       <c r="D32" s="267">
-        <v>1.53</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="E32" s="268">
-        <v>0.127</v>
+        <v>0.152</v>
       </c>
       <c r="F32" s="269">
-        <v>0.75424939999999996</v>
+        <v>0.70598749999999999</v>
       </c>
       <c r="G32" s="270">
-        <v>9.7014750000000003</v>
+        <v>9.3389039999999994</v>
       </c>
     </row>
     <row r="33">
@@ -15231,22 +15231,22 @@
         <v>1</v>
       </c>
       <c r="B35" s="289">
-        <v>2.1310359999999999</v>
+        <v>2.132736</v>
       </c>
       <c r="C35" s="290">
-        <v>2.0713469999999998</v>
+        <v>2.0767509999999998</v>
       </c>
       <c r="D35" s="291">
         <v>0.78000000000000003</v>
       </c>
       <c r="E35" s="292">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="F35" s="293">
-        <v>0.3171254</v>
+        <v>0.3162857</v>
       </c>
       <c r="G35" s="294">
-        <v>14.32025</v>
+        <v>14.381180000000001</v>
       </c>
     </row>
     <row r="36">
@@ -15300,10 +15300,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="313">
-        <v>2.1599999999999999e+32</v>
+        <v>1.8299999999999999e+32</v>
       </c>
       <c r="C38" s="314">
-        <v>2.0699999999999999e+38</v>
+        <v>1.7199999999999999e+38</v>
       </c>
       <c r="D38" s="315">
         <v>0</v>
@@ -15369,10 +15369,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="337">
-        <v>4.0800000000000001e+48</v>
+        <v>6.1599999999999998e+48</v>
       </c>
       <c r="C41" s="338">
-        <v>1.64e+52</v>
+        <v>2.4699999999999999e+52</v>
       </c>
       <c r="D41" s="339">
         <v>0.029999999999999999</v>
@@ -15438,22 +15438,22 @@
         <v>1</v>
       </c>
       <c r="B44" s="361">
-        <v>3.6500000000000002e-06</v>
+        <v>5.2800000000000003e-06</v>
       </c>
       <c r="C44" s="362">
-        <v>6.6699999999999995e-05</v>
+        <v>9.6700000000000006e-05</v>
       </c>
       <c r="D44" s="363">
-        <v>-0.68000000000000005</v>
+        <v>-0.66000000000000003</v>
       </c>
       <c r="E44" s="364">
-        <v>0.494</v>
+        <v>0.50700000000000001</v>
       </c>
       <c r="F44" s="365">
-        <v>9.5299999999999994e-22</v>
+        <v>1.4e-21</v>
       </c>
       <c r="G44" s="366">
-        <v>14000000000</v>
+        <v>19900000000</v>
       </c>
     </row>
     <row r="45">
@@ -15507,22 +15507,22 @@
         <v>1</v>
       </c>
       <c r="B47" s="385">
-        <v>0.1837316</v>
+        <v>0.18547810000000001</v>
       </c>
       <c r="C47" s="386">
-        <v>0.71849399999999997</v>
+        <v>0.73485820000000002</v>
       </c>
       <c r="D47" s="387">
         <v>-0.42999999999999999</v>
       </c>
       <c r="E47" s="388">
-        <v>0.66500000000000004</v>
+        <v>0.67100000000000004</v>
       </c>
       <c r="F47" s="389">
-        <v>8.6199999999999995e-05</v>
+        <v>7.8700000000000002e-05</v>
       </c>
       <c r="G47" s="390">
-        <v>391.61660000000001</v>
+        <v>437.2448</v>
       </c>
     </row>
     <row r="48">
@@ -15576,22 +15576,22 @@
         <v>31</v>
       </c>
       <c r="B50" s="409">
-        <v>0.59599639999999998</v>
+        <v>0.55105599999999999</v>
       </c>
       <c r="C50" s="410">
-        <v>0.14095099999999999</v>
+        <v>0.13419690000000001</v>
       </c>
       <c r="D50" s="411">
-        <v>-2.19</v>
+        <v>-2.4500000000000002</v>
       </c>
       <c r="E50" s="412">
-        <v>0.029000000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="F50" s="413">
-        <v>0.37491910000000001</v>
+        <v>0.34190490000000001</v>
       </c>
       <c r="G50" s="414">
-        <v>0.94743560000000004</v>
+        <v>0.88814939999999998</v>
       </c>
     </row>
     <row r="51">
@@ -15622,22 +15622,22 @@
         <v>34</v>
       </c>
       <c r="B52" s="425">
-        <v>0.14623630000000001</v>
+        <v>0.13269619999999999</v>
       </c>
       <c r="C52" s="426">
-        <v>0.077725199999999994</v>
+        <v>0.071295800000000006</v>
       </c>
       <c r="D52" s="427">
-        <v>-3.6200000000000001</v>
+        <v>-3.7599999999999998</v>
       </c>
       <c r="E52" s="428">
         <v>0</v>
       </c>
       <c r="F52" s="429">
-        <v>0.051598600000000001</v>
+        <v>0.046293399999999999</v>
       </c>
       <c r="G52" s="430">
-        <v>0.41444999999999999</v>
+        <v>0.38036209999999998</v>
       </c>
     </row>
     <row r="53">
@@ -15691,22 +15691,22 @@
         <v>31</v>
       </c>
       <c r="B55" s="449">
-        <v>0.66730319999999999</v>
+        <v>0.65779370000000004</v>
       </c>
       <c r="C55" s="450">
-        <v>0.074409699999999995</v>
+        <v>0.074168399999999996</v>
       </c>
       <c r="D55" s="451">
-        <v>-3.6299999999999999</v>
+        <v>-3.71</v>
       </c>
       <c r="E55" s="452">
         <v>0</v>
       </c>
       <c r="F55" s="453">
-        <v>0.53629939999999998</v>
+        <v>0.52736819999999995</v>
       </c>
       <c r="G55" s="454">
-        <v>0.83030769999999998</v>
+        <v>0.82047519999999996</v>
       </c>
     </row>
     <row r="56">
@@ -15714,22 +15714,22 @@
         <v>32</v>
       </c>
       <c r="B56" s="457">
-        <v>1.4893529999999999</v>
+        <v>1.567612</v>
       </c>
       <c r="C56" s="458">
-        <v>0.63418019999999997</v>
+        <v>0.68369760000000002</v>
       </c>
       <c r="D56" s="459">
-        <v>0.93999999999999995</v>
+        <v>1.03</v>
       </c>
       <c r="E56" s="460">
-        <v>0.34999999999999998</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="F56" s="461">
-        <v>0.64646950000000003</v>
+        <v>0.66680079999999997</v>
       </c>
       <c r="G56" s="462">
-        <v>3.4312079999999998</v>
+        <v>3.685371</v>
       </c>
     </row>
     <row r="57">
@@ -15737,22 +15737,22 @@
         <v>34</v>
       </c>
       <c r="B57" s="465">
-        <v>0.28909750000000001</v>
+        <v>0.25100410000000001</v>
       </c>
       <c r="C57" s="466">
-        <v>0.095009099999999999</v>
+        <v>0.085317900000000002</v>
       </c>
       <c r="D57" s="467">
-        <v>-3.7799999999999998</v>
+        <v>-4.0700000000000003</v>
       </c>
       <c r="E57" s="468">
         <v>0</v>
       </c>
       <c r="F57" s="469">
-        <v>0.15181159999999999</v>
+        <v>0.1289294</v>
       </c>
       <c r="G57" s="470">
-        <v>0.55053339999999995</v>
+        <v>0.48866310000000002</v>
       </c>
     </row>
     <row r="58">
@@ -15806,22 +15806,22 @@
         <v>31</v>
       </c>
       <c r="B60" s="489">
-        <v>0.70087370000000004</v>
+        <v>0.60869010000000001</v>
       </c>
       <c r="C60" s="490">
-        <v>0.25395790000000001</v>
+        <v>0.229707</v>
       </c>
       <c r="D60" s="491">
-        <v>-0.97999999999999998</v>
+        <v>-1.3200000000000001</v>
       </c>
       <c r="E60" s="492">
-        <v>0.32700000000000001</v>
+        <v>0.188</v>
       </c>
       <c r="F60" s="493">
-        <v>0.34451749999999998</v>
+        <v>0.29051630000000001</v>
       </c>
       <c r="G60" s="494">
-        <v>1.4258310000000001</v>
+        <v>1.275328</v>
       </c>
     </row>
     <row r="61">
@@ -15829,22 +15829,22 @@
         <v>32</v>
       </c>
       <c r="B61" s="497">
-        <v>0.83119339999999997</v>
+        <v>0.78761490000000001</v>
       </c>
       <c r="C61" s="498">
-        <v>0.41515020000000002</v>
+        <v>0.4034353</v>
       </c>
       <c r="D61" s="499">
-        <v>-0.37</v>
+        <v>-0.46999999999999997</v>
       </c>
       <c r="E61" s="500">
-        <v>0.71099999999999997</v>
+        <v>0.64100000000000001</v>
       </c>
       <c r="F61" s="501">
-        <v>0.31229030000000002</v>
+        <v>0.28860770000000002</v>
       </c>
       <c r="G61" s="502">
-        <v>2.2123080000000002</v>
+        <v>2.149413</v>
       </c>
     </row>
     <row r="62">
@@ -15852,22 +15852,22 @@
         <v>34</v>
       </c>
       <c r="B62" s="505">
-        <v>0.35956640000000001</v>
+        <v>0.33786359999999999</v>
       </c>
       <c r="C62" s="506">
-        <v>0.21079870000000001</v>
+        <v>0.20027310000000001</v>
       </c>
       <c r="D62" s="507">
-        <v>-1.74</v>
+        <v>-1.8300000000000001</v>
       </c>
       <c r="E62" s="508">
-        <v>0.081000000000000003</v>
+        <v>0.067000000000000004</v>
       </c>
       <c r="F62" s="509">
-        <v>0.1139608</v>
+        <v>0.1057256</v>
       </c>
       <c r="G62" s="510">
-        <v>1.134496</v>
+        <v>1.079698</v>
       </c>
     </row>
     <row r="63">
@@ -15898,22 +15898,22 @@
         <v>37</v>
       </c>
       <c r="B64" s="521">
-        <v>0.68162529999999999</v>
+        <v>0.68247469999999999</v>
       </c>
       <c r="C64" s="522">
-        <v>0.077681399999999998</v>
+        <v>0.078316499999999997</v>
       </c>
       <c r="D64" s="523">
-        <v>-3.3599999999999999</v>
+        <v>-3.3300000000000001</v>
       </c>
       <c r="E64" s="524">
         <v>0.001</v>
       </c>
       <c r="F64" s="525">
-        <v>0.5451783</v>
+        <v>0.54501449999999996</v>
       </c>
       <c r="G64" s="526">
-        <v>0.85222220000000004</v>
+        <v>0.85460440000000004</v>
       </c>
     </row>
     <row r="65">
@@ -15921,22 +15921,22 @@
         <v>38</v>
       </c>
       <c r="B65" s="529">
-        <v>0.99637609999999999</v>
+        <v>0.99661390000000005</v>
       </c>
       <c r="C65" s="530">
-        <v>0.0555229</v>
+        <v>0.056085799999999998</v>
       </c>
       <c r="D65" s="531">
-        <v>-0.070000000000000007</v>
+        <v>-0.059999999999999998</v>
       </c>
       <c r="E65" s="532">
-        <v>0.94799999999999995</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="F65" s="533">
-        <v>0.89328540000000001</v>
+        <v>0.89253320000000003</v>
       </c>
       <c r="G65" s="534">
-        <v>1.111364</v>
+        <v>1.112832</v>
       </c>
     </row>
     <row r="66">
@@ -15944,22 +15944,22 @@
         <v>39</v>
       </c>
       <c r="B66" s="537">
-        <v>0.41179139999999998</v>
+        <v>0.41827809999999999</v>
       </c>
       <c r="C66" s="538">
-        <v>0.034279999999999998</v>
+        <v>0.035176199999999998</v>
       </c>
       <c r="D66" s="539">
-        <v>-10.66</v>
+        <v>-10.359999999999999</v>
       </c>
       <c r="E66" s="540">
         <v>0</v>
       </c>
       <c r="F66" s="541">
-        <v>0.34979870000000002</v>
+        <v>0.35471619999999998</v>
       </c>
       <c r="G66" s="542">
-        <v>0.4847706</v>
+        <v>0.49322959999999999</v>
       </c>
     </row>
     <row r="67">
@@ -15967,22 +15967,22 @@
         <v>40</v>
       </c>
       <c r="B67" s="545">
-        <v>0.655308</v>
+        <v>0.67441220000000002</v>
       </c>
       <c r="C67" s="546">
-        <v>0.045558500000000002</v>
+        <v>0.047351600000000001</v>
       </c>
       <c r="D67" s="547">
-        <v>-6.0800000000000001</v>
+        <v>-5.6100000000000003</v>
       </c>
       <c r="E67" s="548">
         <v>0</v>
       </c>
       <c r="F67" s="549">
-        <v>0.57183130000000004</v>
+        <v>0.58770730000000004</v>
       </c>
       <c r="G67" s="550">
-        <v>0.75097069999999999</v>
+        <v>0.77390859999999995</v>
       </c>
     </row>
     <row r="68">
@@ -15990,22 +15990,22 @@
         <v>41</v>
       </c>
       <c r="B68" s="553">
-        <v>1.1490659999999999</v>
+        <v>1.183899</v>
       </c>
       <c r="C68" s="554">
-        <v>0.083302799999999996</v>
+        <v>0.086713499999999999</v>
       </c>
       <c r="D68" s="555">
-        <v>1.9199999999999999</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E68" s="556">
-        <v>0.055</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="F68" s="557">
-        <v>0.99686459999999999</v>
+        <v>1.025579</v>
       </c>
       <c r="G68" s="558">
-        <v>1.324506</v>
+        <v>1.3666579999999999</v>
       </c>
     </row>
     <row r="69">
@@ -16013,22 +16013,22 @@
         <v>42</v>
       </c>
       <c r="B69" s="561">
-        <v>1.610099</v>
+        <v>1.655035</v>
       </c>
       <c r="C69" s="562">
-        <v>0.12814310000000001</v>
+        <v>0.13311429999999999</v>
       </c>
       <c r="D69" s="563">
-        <v>5.9800000000000004</v>
+        <v>6.2599999999999998</v>
       </c>
       <c r="E69" s="564">
         <v>0</v>
       </c>
       <c r="F69" s="565">
-        <v>1.3775520000000001</v>
+        <v>1.4136599999999999</v>
       </c>
       <c r="G69" s="566">
-        <v>1.881904</v>
+        <v>1.9376230000000001</v>
       </c>
     </row>
     <row r="70">
@@ -16036,22 +16036,22 @@
         <v>43</v>
       </c>
       <c r="B70" s="569">
-        <v>1.914703</v>
+        <v>1.9799519999999999</v>
       </c>
       <c r="C70" s="570">
-        <v>0.31005709999999998</v>
+        <v>0.32220520000000002</v>
       </c>
       <c r="D70" s="571">
-        <v>4.0099999999999998</v>
+        <v>4.2000000000000002</v>
       </c>
       <c r="E70" s="572">
         <v>0</v>
       </c>
       <c r="F70" s="573">
-        <v>1.393999</v>
+        <v>1.439247</v>
       </c>
       <c r="G70" s="574">
-        <v>2.6299090000000001</v>
+        <v>2.723792</v>
       </c>
     </row>
     <row r="71">
@@ -16059,22 +16059,22 @@
         <v>44</v>
       </c>
       <c r="B71" s="577">
-        <v>0.79655390000000004</v>
+        <v>0.78393539999999995</v>
       </c>
       <c r="C71" s="578">
-        <v>0.086888999999999994</v>
+        <v>0.086488899999999994</v>
       </c>
       <c r="D71" s="579">
-        <v>-2.0899999999999999</v>
+        <v>-2.21</v>
       </c>
       <c r="E71" s="580">
-        <v>0.036999999999999998</v>
+        <v>0.027</v>
       </c>
       <c r="F71" s="581">
-        <v>0.64322829999999998</v>
+        <v>0.63149540000000004</v>
       </c>
       <c r="G71" s="582">
-        <v>0.98642770000000002</v>
+        <v>0.97317390000000004</v>
       </c>
     </row>
     <row r="72">
@@ -16082,22 +16082,22 @@
         <v>45</v>
       </c>
       <c r="B72" s="585">
-        <v>0.65304249999999997</v>
+        <v>0.64677640000000003</v>
       </c>
       <c r="C72" s="586">
-        <v>0.067691899999999999</v>
+        <v>0.067735699999999996</v>
       </c>
       <c r="D72" s="587">
-        <v>-4.1100000000000003</v>
+        <v>-4.1600000000000001</v>
       </c>
       <c r="E72" s="588">
         <v>0</v>
       </c>
       <c r="F72" s="589">
-        <v>0.53297779999999995</v>
+        <v>0.52675590000000006</v>
       </c>
       <c r="G72" s="590">
-        <v>0.80015440000000004</v>
+        <v>0.7941435</v>
       </c>
     </row>
     <row r="73">
@@ -16105,22 +16105,22 @@
         <v>46</v>
       </c>
       <c r="B73" s="593">
-        <v>0.605993</v>
+        <v>0.58532220000000001</v>
       </c>
       <c r="C73" s="594">
-        <v>0.14290149999999999</v>
+        <v>0.14381450000000001</v>
       </c>
       <c r="D73" s="595">
-        <v>-2.1200000000000001</v>
+        <v>-2.1800000000000002</v>
       </c>
       <c r="E73" s="596">
-        <v>0.034000000000000002</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="F73" s="597">
-        <v>0.3817179</v>
+        <v>0.36162090000000002</v>
       </c>
       <c r="G73" s="598">
-        <v>0.96203910000000004</v>
+        <v>0.94740670000000005</v>
       </c>
     </row>
     <row r="74">
@@ -16128,22 +16128,22 @@
         <v>47</v>
       </c>
       <c r="B74" s="601">
-        <v>0.83675259999999996</v>
+        <v>0.85575290000000004</v>
       </c>
       <c r="C74" s="602">
-        <v>0.1037848</v>
+        <v>0.10715710000000001</v>
       </c>
       <c r="D74" s="603">
-        <v>-1.44</v>
+        <v>-1.24</v>
       </c>
       <c r="E74" s="604">
-        <v>0.151</v>
+        <v>0.213</v>
       </c>
       <c r="F74" s="605">
-        <v>0.65617570000000003</v>
+        <v>0.66951649999999996</v>
       </c>
       <c r="G74" s="606">
-        <v>1.067024</v>
+        <v>1.0937939999999999</v>
       </c>
     </row>
     <row r="75">
@@ -16151,22 +16151,22 @@
         <v>48</v>
       </c>
       <c r="B75" s="609">
-        <v>1.122288</v>
+        <v>0.89077490000000004</v>
       </c>
       <c r="C75" s="610">
-        <v>0.016030599999999999</v>
+        <v>0.012821600000000001</v>
       </c>
       <c r="D75" s="611">
-        <v>8.0800000000000001</v>
+        <v>-8.0399999999999991</v>
       </c>
       <c r="E75" s="612">
         <v>0</v>
       </c>
       <c r="F75" s="613">
-        <v>1.0913040000000001</v>
+        <v>0.86599610000000005</v>
       </c>
       <c r="G75" s="614">
-        <v>1.1541509999999999</v>
+        <v>0.91626260000000004</v>
       </c>
     </row>
     <row r="76">
@@ -16174,22 +16174,22 @@
         <v>49</v>
       </c>
       <c r="B76" s="617">
-        <v>0.99968690000000004</v>
+        <v>0.90684299999999996</v>
       </c>
       <c r="C76" s="618">
-        <v>0.0023747999999999998</v>
+        <v>0.1370044</v>
       </c>
       <c r="D76" s="619">
-        <v>-0.13</v>
+        <v>-0.65000000000000002</v>
       </c>
       <c r="E76" s="620">
-        <v>0.89500000000000002</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="F76" s="621">
-        <v>0.99504329999999996</v>
+        <v>0.67442539999999995</v>
       </c>
       <c r="G76" s="622">
-        <v>1.0043519999999999</v>
+        <v>1.219355</v>
       </c>
     </row>
     <row r="77">
@@ -16197,22 +16197,22 @@
         <v>50</v>
       </c>
       <c r="B77" s="625">
-        <v>0.87272170000000004</v>
+        <v>0.86325620000000003</v>
       </c>
       <c r="C77" s="626">
-        <v>0.061961200000000001</v>
+        <v>0.061733299999999998</v>
       </c>
       <c r="D77" s="627">
-        <v>-1.9199999999999999</v>
+        <v>-2.0600000000000001</v>
       </c>
       <c r="E77" s="628">
-        <v>0.055</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="F77" s="629">
-        <v>0.75935070000000005</v>
+        <v>0.75035790000000002</v>
       </c>
       <c r="G77" s="630">
-        <v>1.0030190000000001</v>
+        <v>0.99314119999999995</v>
       </c>
     </row>
     <row r="78">
@@ -16220,22 +16220,22 @@
         <v>51</v>
       </c>
       <c r="B78" s="633">
-        <v>0.60987809999999998</v>
+        <v>0.59941259999999996</v>
       </c>
       <c r="C78" s="634">
-        <v>0.096645599999999998</v>
+        <v>0.095812300000000003</v>
       </c>
       <c r="D78" s="635">
-        <v>-3.1200000000000001</v>
+        <v>-3.2000000000000002</v>
       </c>
       <c r="E78" s="636">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F78" s="637">
-        <v>0.44704949999999999</v>
+        <v>0.43819429999999998</v>
       </c>
       <c r="G78" s="638">
-        <v>0.83201369999999997</v>
+        <v>0.81994549999999999</v>
       </c>
     </row>
     <row r="79">
@@ -16243,22 +16243,22 @@
         <v>52</v>
       </c>
       <c r="B79" s="641">
-        <v>0.75286819999999999</v>
+        <v>0.7522316</v>
       </c>
       <c r="C79" s="642">
-        <v>0.072814000000000004</v>
+        <v>0.073402999999999996</v>
       </c>
       <c r="D79" s="643">
-        <v>-2.94</v>
+        <v>-2.9199999999999999</v>
       </c>
       <c r="E79" s="644">
-        <v>0.0030000000000000001</v>
+        <v>0.0040000000000000001</v>
       </c>
       <c r="F79" s="645">
-        <v>0.62286600000000003</v>
+        <v>0.62128530000000004</v>
       </c>
       <c r="G79" s="646">
-        <v>0.91000400000000004</v>
+        <v>0.91077699999999995</v>
       </c>
     </row>
     <row r="80">
@@ -16266,22 +16266,22 @@
         <v>53</v>
       </c>
       <c r="B80" s="649">
-        <v>0.83349549999999995</v>
+        <v>0.82922549999999995</v>
       </c>
       <c r="C80" s="650">
-        <v>0.077755500000000005</v>
+        <v>0.077998300000000007</v>
       </c>
       <c r="D80" s="651">
-        <v>-1.95</v>
+        <v>-1.99</v>
       </c>
       <c r="E80" s="652">
-        <v>0.050999999999999997</v>
+        <v>0.045999999999999999</v>
       </c>
       <c r="F80" s="653">
-        <v>0.69421820000000001</v>
+        <v>0.68961589999999995</v>
       </c>
       <c r="G80" s="654">
-        <v>1.000715</v>
+        <v>0.99709840000000005</v>
       </c>
     </row>
     <row r="81">
@@ -16289,22 +16289,22 @@
         <v>54</v>
       </c>
       <c r="B81" s="657">
-        <v>1.167262</v>
+        <v>1.09552</v>
       </c>
       <c r="C81" s="658">
-        <v>0.81451810000000002</v>
+        <v>0.7683797</v>
       </c>
       <c r="D81" s="659">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="E81" s="660">
-        <v>0.82499999999999996</v>
+        <v>0.89700000000000002</v>
       </c>
       <c r="F81" s="661">
-        <v>0.29730210000000001</v>
+        <v>0.27707739999999997</v>
       </c>
       <c r="G81" s="662">
-        <v>4.5828829999999998</v>
+        <v>4.3315080000000004</v>
       </c>
     </row>
     <row r="82">
@@ -16312,22 +16312,22 @@
         <v>55</v>
       </c>
       <c r="B82" s="665">
-        <v>1.2495970000000001</v>
+        <v>1.2366900000000001</v>
       </c>
       <c r="C82" s="666">
-        <v>0.052612100000000002</v>
+        <v>0.052577800000000001</v>
       </c>
       <c r="D82" s="667">
-        <v>5.29</v>
+        <v>5</v>
       </c>
       <c r="E82" s="668">
         <v>0</v>
       </c>
       <c r="F82" s="669">
-        <v>1.1506190000000001</v>
+        <v>1.1378159999999999</v>
       </c>
       <c r="G82" s="670">
-        <v>1.357089</v>
+        <v>1.3441559999999999</v>
       </c>
     </row>
     <row r="83">
@@ -16335,22 +16335,22 @@
         <v>56</v>
       </c>
       <c r="B83" s="673">
-        <v>0.99889430000000001</v>
+        <v>0.87248959999999998</v>
       </c>
       <c r="C83" s="674">
-        <v>0.00047600000000000002</v>
+        <v>0.024729600000000001</v>
       </c>
       <c r="D83" s="675">
-        <v>-2.3199999999999999</v>
+        <v>-4.8099999999999996</v>
       </c>
       <c r="E83" s="676">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F83" s="677">
-        <v>0.99796180000000001</v>
+        <v>0.82534209999999997</v>
       </c>
       <c r="G83" s="678">
-        <v>0.99982769999999999</v>
+        <v>0.92233030000000005</v>
       </c>
     </row>
     <row r="84">
@@ -16358,22 +16358,22 @@
         <v>57</v>
       </c>
       <c r="B84" s="681">
-        <v>0.75205089999999997</v>
+        <v>0.74381870000000005</v>
       </c>
       <c r="C84" s="682">
-        <v>0.047179899999999997</v>
+        <v>0.047254600000000001</v>
       </c>
       <c r="D84" s="683">
-        <v>-4.54</v>
+        <v>-4.6600000000000001</v>
       </c>
       <c r="E84" s="684">
         <v>0</v>
       </c>
       <c r="F84" s="685">
-        <v>0.66503900000000005</v>
+        <v>0.65673539999999997</v>
       </c>
       <c r="G84" s="686">
-        <v>0.85044719999999996</v>
+        <v>0.84244920000000001</v>
       </c>
     </row>
     <row r="85">
@@ -16381,22 +16381,22 @@
         <v>58</v>
       </c>
       <c r="B85" s="689">
-        <v>0.9560613</v>
+        <v>0.94648120000000002</v>
       </c>
       <c r="C85" s="690">
-        <v>0.081471100000000005</v>
+        <v>0.081426399999999996</v>
       </c>
       <c r="D85" s="691">
-        <v>-0.53000000000000003</v>
+        <v>-0.64000000000000001</v>
       </c>
       <c r="E85" s="692">
-        <v>0.59799999999999998</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="F85" s="693">
-        <v>0.80900340000000004</v>
+        <v>0.79961800000000005</v>
       </c>
       <c r="G85" s="694">
-        <v>1.1298509999999999</v>
+        <v>1.1203179999999999</v>
       </c>
     </row>
     <row r="86">
@@ -16404,22 +16404,22 @@
         <v>59</v>
       </c>
       <c r="B86" s="697">
-        <v>0.7229582</v>
+        <v>0.72570619999999997</v>
       </c>
       <c r="C86" s="698">
-        <v>0.0330832</v>
+        <v>0.0335494</v>
       </c>
       <c r="D86" s="699">
-        <v>-7.0899999999999999</v>
+        <v>-6.9400000000000004</v>
       </c>
       <c r="E86" s="700">
         <v>0</v>
       </c>
       <c r="F86" s="701">
-        <v>0.6609391</v>
+        <v>0.66284160000000003</v>
       </c>
       <c r="G86" s="702">
-        <v>0.79079690000000002</v>
+        <v>0.79453300000000004</v>
       </c>
     </row>
     <row r="87">
@@ -16427,22 +16427,22 @@
         <v>60</v>
       </c>
       <c r="B87" s="705">
-        <v>1.035914</v>
+        <v>1.0453730000000001</v>
       </c>
       <c r="C87" s="706">
-        <v>0.1048149</v>
+        <v>0.1062951</v>
       </c>
       <c r="D87" s="707">
-        <v>0.34999999999999998</v>
+        <v>0.44</v>
       </c>
       <c r="E87" s="708">
-        <v>0.72699999999999998</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="F87" s="709">
-        <v>0.84956810000000005</v>
+        <v>0.85648489999999999</v>
       </c>
       <c r="G87" s="710">
-        <v>1.2631330000000001</v>
+        <v>1.2759180000000001</v>
       </c>
     </row>
     <row r="88">
@@ -16450,22 +16450,22 @@
         <v>61</v>
       </c>
       <c r="B88" s="713">
-        <v>0.83730090000000001</v>
+        <v>0.830484</v>
       </c>
       <c r="C88" s="714">
-        <v>0.071672299999999994</v>
+        <v>0.071804000000000007</v>
       </c>
       <c r="D88" s="715">
-        <v>-2.0699999999999999</v>
+        <v>-2.1499999999999999</v>
       </c>
       <c r="E88" s="716">
-        <v>0.037999999999999999</v>
+        <v>0.032000000000000001</v>
       </c>
       <c r="F88" s="717">
-        <v>0.70797730000000003</v>
+        <v>0.70102909999999996</v>
       </c>
       <c r="G88" s="718">
-        <v>0.9902474</v>
+        <v>0.98384459999999996</v>
       </c>
     </row>
     <row r="89">
@@ -16473,22 +16473,22 @@
         <v>62</v>
       </c>
       <c r="B89" s="721">
-        <v>0.99252359999999995</v>
+        <v>0.9960658</v>
       </c>
       <c r="C89" s="722">
-        <v>0.042461699999999998</v>
+        <v>0.0430286</v>
       </c>
       <c r="D89" s="723">
-        <v>-0.17999999999999999</v>
+        <v>-0.089999999999999997</v>
       </c>
       <c r="E89" s="724">
-        <v>0.86099999999999999</v>
+        <v>0.92700000000000005</v>
       </c>
       <c r="F89" s="725">
-        <v>0.91269389999999995</v>
+        <v>0.91520279999999998</v>
       </c>
       <c r="G89" s="726">
-        <v>1.0793360000000001</v>
+        <v>1.0840730000000001</v>
       </c>
     </row>
     <row r="90">
@@ -16496,22 +16496,22 @@
         <v>63</v>
       </c>
       <c r="B90" s="729">
-        <v>0.82234779999999996</v>
+        <v>0.81962270000000004</v>
       </c>
       <c r="C90" s="730">
-        <v>0.0372358</v>
+        <v>0.037519400000000001</v>
       </c>
       <c r="D90" s="731">
-        <v>-4.3200000000000003</v>
+        <v>-4.3499999999999996</v>
       </c>
       <c r="E90" s="732">
         <v>0</v>
       </c>
       <c r="F90" s="733">
-        <v>0.75251170000000001</v>
+        <v>0.74928839999999997</v>
       </c>
       <c r="G90" s="734">
-        <v>0.8986651</v>
+        <v>0.89655910000000005</v>
       </c>
     </row>
     <row r="91">
@@ -16542,22 +16542,22 @@
         <v>66</v>
       </c>
       <c r="B92" s="745">
-        <v>0.59504630000000003</v>
+        <v>0.62555179999999999</v>
       </c>
       <c r="C92" s="746">
-        <v>0.1052738</v>
+        <v>0.1172286</v>
       </c>
       <c r="D92" s="747">
-        <v>-2.9300000000000002</v>
+        <v>-2.5</v>
       </c>
       <c r="E92" s="748">
-        <v>0.0030000000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="F92" s="749">
-        <v>0.42068660000000002</v>
+        <v>0.43325920000000001</v>
       </c>
       <c r="G92" s="750">
-        <v>0.84167179999999997</v>
+        <v>0.90318909999999997</v>
       </c>
     </row>
     <row r="93">
@@ -16565,22 +16565,22 @@
         <v>67</v>
       </c>
       <c r="B93" s="753">
-        <v>0.85713090000000003</v>
+        <v>0.91712649999999996</v>
       </c>
       <c r="C93" s="754">
-        <v>0.15579779999999999</v>
+        <v>0.1765418</v>
       </c>
       <c r="D93" s="755">
-        <v>-0.84999999999999998</v>
+        <v>-0.45000000000000001</v>
       </c>
       <c r="E93" s="756">
-        <v>0.39600000000000002</v>
+        <v>0.65300000000000002</v>
       </c>
       <c r="F93" s="757">
-        <v>0.60024310000000003</v>
+        <v>0.62889430000000002</v>
       </c>
       <c r="G93" s="758">
-        <v>1.2239599999999999</v>
+        <v>1.3374600000000001</v>
       </c>
     </row>
     <row r="94">
@@ -16588,22 +16588,22 @@
         <v>68</v>
       </c>
       <c r="B94" s="761">
-        <v>0.76771650000000002</v>
+        <v>0.81265969999999999</v>
       </c>
       <c r="C94" s="762">
-        <v>0.12682660000000001</v>
+        <v>0.14326549999999999</v>
       </c>
       <c r="D94" s="763">
-        <v>-1.6000000000000001</v>
+        <v>-1.1799999999999999</v>
       </c>
       <c r="E94" s="764">
-        <v>0.11</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="F94" s="765">
-        <v>0.55537020000000004</v>
+        <v>0.57523930000000001</v>
       </c>
       <c r="G94" s="766">
-        <v>1.0612539999999999</v>
+        <v>1.1480710000000001</v>
       </c>
     </row>
     <row r="95">
@@ -16611,22 +16611,22 @@
         <v>69</v>
       </c>
       <c r="B95" s="769">
-        <v>1.3280000000000001</v>
+        <v>1.4340660000000001</v>
       </c>
       <c r="C95" s="770">
-        <v>0.2133351</v>
+        <v>0.246031</v>
       </c>
       <c r="D95" s="771">
-        <v>1.77</v>
+        <v>2.1000000000000001</v>
       </c>
       <c r="E95" s="772">
-        <v>0.076999999999999999</v>
+        <v>0.035999999999999997</v>
       </c>
       <c r="F95" s="773">
-        <v>0.96929880000000002</v>
+        <v>1.0245550000000001</v>
       </c>
       <c r="G95" s="774">
-        <v>1.8194429999999999</v>
+        <v>2.0072559999999999</v>
       </c>
     </row>
     <row r="96">
@@ -16657,22 +16657,22 @@
         <v>71</v>
       </c>
       <c r="B97" s="785">
-        <v>0.77839049999999999</v>
+        <v>0.78630730000000004</v>
       </c>
       <c r="C97" s="786">
-        <v>0.056613400000000001</v>
+        <v>0.057783899999999999</v>
       </c>
       <c r="D97" s="787">
-        <v>-3.44</v>
+        <v>-3.27</v>
       </c>
       <c r="E97" s="788">
         <v>0.001</v>
       </c>
       <c r="F97" s="789">
-        <v>0.67497620000000003</v>
+        <v>0.68083119999999997</v>
       </c>
       <c r="G97" s="790">
-        <v>0.89764909999999998</v>
+        <v>0.90812400000000004</v>
       </c>
     </row>
     <row r="98">
@@ -16680,22 +16680,22 @@
         <v>72</v>
       </c>
       <c r="B98" s="793">
-        <v>0.79834530000000004</v>
+        <v>0.80465629999999999</v>
       </c>
       <c r="C98" s="794">
-        <v>0.067584099999999994</v>
+        <v>0.068797499999999998</v>
       </c>
       <c r="D98" s="795">
-        <v>-2.6600000000000001</v>
+        <v>-2.54</v>
       </c>
       <c r="E98" s="796">
-        <v>0.0080000000000000002</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="F98" s="797">
-        <v>0.67628880000000002</v>
+        <v>0.68050809999999995</v>
       </c>
       <c r="G98" s="798">
-        <v>0.94243069999999996</v>
+        <v>0.95145329999999995</v>
       </c>
     </row>
     <row r="99">
@@ -16703,22 +16703,22 @@
         <v>73</v>
       </c>
       <c r="B99" s="801">
-        <v>1.4348350000000001</v>
+        <v>1.4629509999999999</v>
       </c>
       <c r="C99" s="802">
-        <v>0.1884575</v>
+        <v>0.1963086</v>
       </c>
       <c r="D99" s="803">
-        <v>2.75</v>
+        <v>2.8399999999999999</v>
       </c>
       <c r="E99" s="804">
-        <v>0.0060000000000000001</v>
+        <v>0.0050000000000000001</v>
       </c>
       <c r="F99" s="805">
-        <v>1.1091789999999999</v>
+        <v>1.1246309999999999</v>
       </c>
       <c r="G99" s="806">
-        <v>1.8561049999999999</v>
+        <v>1.9030480000000001</v>
       </c>
     </row>
     <row r="100">
@@ -16726,22 +16726,22 @@
         <v>74</v>
       </c>
       <c r="B100" s="809">
-        <v>1.2140310000000001</v>
+        <v>1.286913</v>
       </c>
       <c r="C100" s="810">
-        <v>0.28499259999999999</v>
+        <v>0.3056662</v>
       </c>
       <c r="D100" s="811">
-        <v>0.82999999999999996</v>
+        <v>1.0600000000000001</v>
       </c>
       <c r="E100" s="812">
-        <v>0.40899999999999998</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="F100" s="813">
-        <v>0.76632180000000005</v>
+        <v>0.80792839999999999</v>
       </c>
       <c r="G100" s="814">
-        <v>1.9233070000000001</v>
+        <v>2.0498669999999999</v>
       </c>
     </row>
     <row r="101">
@@ -16749,22 +16749,22 @@
         <v>75</v>
       </c>
       <c r="B101" s="817">
-        <v>1.2101850000000001</v>
+        <v>1.190107</v>
       </c>
       <c r="C101" s="818">
-        <v>0.24924830000000001</v>
+        <v>0.24756990000000001</v>
       </c>
       <c r="D101" s="819">
-        <v>0.93000000000000005</v>
+        <v>0.83999999999999997</v>
       </c>
       <c r="E101" s="820">
-        <v>0.35399999999999998</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="F101" s="821">
-        <v>0.80823789999999995</v>
+        <v>0.79161970000000004</v>
       </c>
       <c r="G101" s="822">
-        <v>1.812025</v>
+        <v>1.7891870000000001</v>
       </c>
     </row>
     <row r="102">
@@ -16772,22 +16772,22 @@
         <v>76</v>
       </c>
       <c r="B102" s="825">
-        <v>2.3225899999999999</v>
+        <v>2.1956419999999999</v>
       </c>
       <c r="C102" s="826">
-        <v>3.499295</v>
+        <v>3.3347280000000001</v>
       </c>
       <c r="D102" s="827">
-        <v>0.56000000000000005</v>
+        <v>0.52000000000000002</v>
       </c>
       <c r="E102" s="828">
-        <v>0.57599999999999996</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="F102" s="829">
-        <v>0.1212056</v>
+        <v>0.11188240000000001</v>
       </c>
       <c r="G102" s="830">
-        <v>44.506390000000003</v>
+        <v>43.088500000000003</v>
       </c>
     </row>
     <row r="103">
@@ -16795,22 +16795,22 @@
         <v>77</v>
       </c>
       <c r="B103" s="833">
-        <v>1.123597</v>
+        <v>1.105046</v>
       </c>
       <c r="C103" s="834">
-        <v>0.10134990000000001</v>
+        <v>0.1019793</v>
       </c>
       <c r="D103" s="835">
-        <v>1.29</v>
+        <v>1.0800000000000001</v>
       </c>
       <c r="E103" s="836">
-        <v>0.19600000000000001</v>
+        <v>0.27900000000000003</v>
       </c>
       <c r="F103" s="837">
-        <v>0.94152389999999997</v>
+        <v>0.92220460000000004</v>
       </c>
       <c r="G103" s="838">
-        <v>1.340881</v>
+        <v>1.324139</v>
       </c>
     </row>
     <row r="104">
@@ -16818,22 +16818,22 @@
         <v>78</v>
       </c>
       <c r="B104" s="841">
-        <v>1.2954490000000001</v>
+        <v>1.2770539999999999</v>
       </c>
       <c r="C104" s="842">
-        <v>0.12661629999999999</v>
+        <v>0.12709719999999999</v>
       </c>
       <c r="D104" s="843">
-        <v>2.6499999999999999</v>
+        <v>2.46</v>
       </c>
       <c r="E104" s="844">
-        <v>0.0080000000000000002</v>
+        <v>0.014</v>
       </c>
       <c r="F104" s="845">
-        <v>1.069607</v>
+        <v>1.050738</v>
       </c>
       <c r="G104" s="846">
-        <v>1.568975</v>
+        <v>1.5521149999999999</v>
       </c>
     </row>
     <row r="105">
@@ -16841,22 +16841,22 @@
         <v>79</v>
       </c>
       <c r="B105" s="849">
-        <v>0.76442710000000003</v>
+        <v>0.74934789999999996</v>
       </c>
       <c r="C105" s="850">
-        <v>0.1045673</v>
+        <v>0.1036937</v>
       </c>
       <c r="D105" s="851">
-        <v>-1.96</v>
+        <v>-2.0899999999999999</v>
       </c>
       <c r="E105" s="852">
-        <v>0.050000000000000003</v>
+        <v>0.036999999999999998</v>
       </c>
       <c r="F105" s="853">
-        <v>0.5846538</v>
+        <v>0.57134110000000005</v>
       </c>
       <c r="G105" s="854">
-        <v>0.99947830000000004</v>
+        <v>0.98281430000000003</v>
       </c>
     </row>
     <row r="106">
@@ -16864,22 +16864,22 @@
         <v>80</v>
       </c>
       <c r="B106" s="857">
-        <v>0.30841069999999998</v>
+        <v>0.29885050000000002</v>
       </c>
       <c r="C106" s="858">
-        <v>0.33499590000000001</v>
+        <v>0.32612570000000002</v>
       </c>
       <c r="D106" s="859">
-        <v>-1.0800000000000001</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="E106" s="860">
-        <v>0.27900000000000003</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="F106" s="861">
-        <v>0.036690500000000001</v>
+        <v>0.035201900000000001</v>
       </c>
       <c r="G106" s="862">
-        <v>2.592419</v>
+        <v>2.5371269999999999</v>
       </c>
     </row>
     <row r="107">
@@ -16887,22 +16887,22 @@
         <v>81</v>
       </c>
       <c r="B107" s="865">
-        <v>1.551202</v>
+        <v>1.493922</v>
       </c>
       <c r="C107" s="866">
-        <v>0.2536175</v>
+        <v>0.25169750000000002</v>
       </c>
       <c r="D107" s="867">
-        <v>2.69</v>
+        <v>2.3799999999999999</v>
       </c>
       <c r="E107" s="868">
-        <v>0.0070000000000000001</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="F107" s="869">
-        <v>1.1258980000000001</v>
+        <v>1.0737829999999999</v>
       </c>
       <c r="G107" s="870">
-        <v>2.1371630000000001</v>
+        <v>2.0784479999999999</v>
       </c>
     </row>
     <row r="108">
@@ -16910,22 +16910,22 @@
         <v>82</v>
       </c>
       <c r="B108" s="873">
-        <v>0.72384970000000004</v>
+        <v>0.7267247</v>
       </c>
       <c r="C108" s="874">
-        <v>0.21128839999999999</v>
+        <v>0.2133931</v>
       </c>
       <c r="D108" s="875">
-        <v>-1.1100000000000001</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="E108" s="876">
-        <v>0.26800000000000002</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="F108" s="877">
-        <v>0.40849479999999999</v>
+        <v>0.40872000000000003</v>
       </c>
       <c r="G108" s="878">
-        <v>1.282656</v>
+        <v>1.2921530000000001</v>
       </c>
     </row>
     <row r="109">
@@ -16933,22 +16933,22 @@
         <v>83</v>
       </c>
       <c r="B109" s="881">
-        <v>0.64589770000000002</v>
+        <v>0.636073</v>
       </c>
       <c r="C109" s="882">
-        <v>0.0889408</v>
+        <v>0.089881699999999995</v>
       </c>
       <c r="D109" s="883">
-        <v>-3.1699999999999999</v>
+        <v>-3.2000000000000002</v>
       </c>
       <c r="E109" s="884">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F109" s="885">
-        <v>0.4931198</v>
+        <v>0.48219869999999998</v>
       </c>
       <c r="G109" s="886">
-        <v>0.84600920000000002</v>
+        <v>0.83904999999999996</v>
       </c>
     </row>
     <row r="110">
@@ -16956,22 +16956,22 @@
         <v>84</v>
       </c>
       <c r="B110" s="889">
-        <v>1.2716609999999999</v>
+        <v>1.3131029999999999</v>
       </c>
       <c r="C110" s="890">
-        <v>0.2203859</v>
+        <v>0.2284378</v>
       </c>
       <c r="D110" s="891">
-        <v>1.3899999999999999</v>
+        <v>1.5700000000000001</v>
       </c>
       <c r="E110" s="892">
-        <v>0.16600000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="F110" s="893">
-        <v>0.90542739999999999</v>
+        <v>0.93372100000000002</v>
       </c>
       <c r="G110" s="894">
-        <v>1.786033</v>
+        <v>1.846633</v>
       </c>
     </row>
     <row r="111">
@@ -16979,22 +16979,22 @@
         <v>85</v>
       </c>
       <c r="B111" s="897">
-        <v>1.0239579999999999</v>
+        <v>1.0182089999999999</v>
       </c>
       <c r="C111" s="898">
-        <v>0.062908400000000003</v>
+        <v>0.0633465</v>
       </c>
       <c r="D111" s="899">
-        <v>0.39000000000000001</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E111" s="900">
-        <v>0.69999999999999996</v>
+        <v>0.77200000000000002</v>
       </c>
       <c r="F111" s="901">
-        <v>0.90779359999999998</v>
+        <v>0.90132330000000005</v>
       </c>
       <c r="G111" s="902">
-        <v>1.1549860000000001</v>
+        <v>1.150253</v>
       </c>
     </row>
     <row r="112">
@@ -17002,22 +17002,22 @@
         <v>86</v>
       </c>
       <c r="B112" s="905">
-        <v>1.031685</v>
+        <v>1.1065430000000001</v>
       </c>
       <c r="C112" s="906">
-        <v>0.16740269999999999</v>
+        <v>0.18672230000000001</v>
       </c>
       <c r="D112" s="907">
-        <v>0.19</v>
+        <v>0.59999999999999998</v>
       </c>
       <c r="E112" s="908">
-        <v>0.84799999999999998</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="F112" s="909">
-        <v>0.75063709999999995</v>
+        <v>0.79493769999999997</v>
       </c>
       <c r="G112" s="910">
-        <v>1.417961</v>
+        <v>1.5402929999999999</v>
       </c>
     </row>
     <row r="113">
@@ -17025,22 +17025,22 @@
         <v>87</v>
       </c>
       <c r="B113" s="913">
-        <v>0.97612279999999996</v>
+        <v>0.97129080000000001</v>
       </c>
       <c r="C113" s="914">
-        <v>0.084492499999999998</v>
+        <v>0.084485900000000003</v>
       </c>
       <c r="D113" s="915">
-        <v>-0.28000000000000003</v>
+        <v>-0.33000000000000002</v>
       </c>
       <c r="E113" s="916">
-        <v>0.78000000000000003</v>
+        <v>0.73799999999999999</v>
       </c>
       <c r="F113" s="917">
-        <v>0.82380620000000004</v>
+        <v>0.81904759999999999</v>
       </c>
       <c r="G113" s="918">
-        <v>1.1566019999999999</v>
+        <v>1.1518330000000001</v>
       </c>
     </row>
     <row r="114">
@@ -17048,22 +17048,22 @@
         <v>88</v>
       </c>
       <c r="B114" s="921">
-        <v>1.425359</v>
+        <v>1.41302</v>
       </c>
       <c r="C114" s="922">
-        <v>0.35041109999999998</v>
+        <v>0.34986339999999999</v>
       </c>
       <c r="D114" s="923">
-        <v>1.44</v>
+        <v>1.3999999999999999</v>
       </c>
       <c r="E114" s="924">
-        <v>0.14899999999999999</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="F114" s="925">
-        <v>0.88036829999999999</v>
+        <v>0.86974359999999995</v>
       </c>
       <c r="G114" s="926">
-        <v>2.3077260000000002</v>
+        <v>2.2956500000000002</v>
       </c>
     </row>
     <row r="115">
@@ -17071,22 +17071,22 @@
         <v>89</v>
       </c>
       <c r="B115" s="936">
-        <v>9e-102</v>
+        <v>4.3321170000000002</v>
       </c>
       <c r="C115" s="937">
-        <v>2.5999999999999999e-100</v>
+        <v>3.303239</v>
       </c>
       <c r="D115" s="938">
-        <v>-8.0800000000000001</v>
+        <v>1.9199999999999999</v>
       </c>
       <c r="E115" s="939">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="F115" s="940">
-        <v>2.7e-126</v>
+        <v>0.97198379999999995</v>
       </c>
       <c r="G115" s="941">
-        <v>3.0199999999999999e-77</v>
+        <v>19.30818</v>
       </c>
     </row>
   </sheetData>

--- a/mortality_odds_only_pdl1.xlsx
+++ b/mortality_odds_only_pdl1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="321" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="356" uniqueCount="91">
   <si>
     <t>mortality_outcome</t>
   </si>
@@ -39,16 +39,16 @@
     <t>io_mono</t>
   </si>
   <si>
-    <t>firstlinechemotherapy</t>
+    <t>firstlinechemothe~y</t>
   </si>
   <si>
-    <t>nonfirstlinechemotherapy</t>
+    <t>nonfirstlinechemo~y</t>
   </si>
   <si>
-    <t>otherfirstlinetherapy</t>
+    <t>otherfirstlinethe~y</t>
   </si>
   <si>
-    <t>firstlinecombinationtherapy</t>
+    <t>firstlinecombinat~y</t>
   </si>
   <si>
     <t>antibrafdrug</t>
@@ -63,10 +63,10 @@
     <t>metinhibitor</t>
   </si>
   <si>
-    <t>carboplatinmonotherapy</t>
+    <t>carboplatinmonoth~y</t>
   </si>
   <si>
-    <t>cisplatinmonotherapy</t>
+    <t>cisplatinmonother~y</t>
   </si>
   <si>
     <t>antialkdrug#alk</t>
@@ -111,10 +111,10 @@
     <t>ecog4</t>
   </si>
   <si>
-    <t>squamouscellcarcinoma</t>
+    <t>squamouscellcarci~a</t>
   </si>
   <si>
-    <t>nonsquamouscellcarcinoma</t>
+    <t>nonsquamouscellca~a</t>
   </si>
   <si>
     <t>pdl1</t>
@@ -147,13 +147,13 @@
     <t>male</t>
   </si>
   <si>
-    <t>daysfromadvanceddiagnosistotreat</t>
+    <t>daysfromadvancedd~t</t>
   </si>
   <si>
-    <t>patientassistanceprogram</t>
+    <t>patientassistance~m</t>
   </si>
   <si>
-    <t>othergovernmentalinsurance</t>
+    <t>othergovernmental~e</t>
   </si>
   <si>
     <t>medicare</t>
@@ -165,7 +165,7 @@
     <t>medicaid</t>
   </si>
   <si>
-    <t>commercialhealthplan</t>
+    <t>commercialhealthp~n</t>
   </si>
   <si>
     <t>noinsurance</t>
@@ -195,7 +195,7 @@
     <t>neversmoker</t>
   </si>
   <si>
-    <t>academicmedicalcenter</t>
+    <t>academicmedicalce~r</t>
   </si>
   <si>
     <t>kidney_bool</t>
@@ -204,10 +204,10 @@
     <t>liver_bool</t>
   </si>
   <si>
-    <t>connective_tissue_bool</t>
+    <t>connective_tissue~l</t>
   </si>
   <si>
-    <t>interstitiallungdisease</t>
+    <t>interstitiallungd~e</t>
   </si>
   <si>
     <t>diabetes</t>
@@ -222,40 +222,43 @@
     <t>othercnsmetastases</t>
   </si>
   <si>
-    <t>digestivesystemmetastases</t>
+    <t>digestivesystemme~s</t>
   </si>
   <si>
     <t>adrenalmetastases</t>
   </si>
   <si>
-    <t>unspecifiedmetastases</t>
+    <t>unspecifiedmetast~s</t>
   </si>
   <si>
-    <t>antiinfectiveusepriortotreatment</t>
+    <t>antiinfectiveusep~t</t>
   </si>
   <si>
-    <t>glucocorticoidusepriortotreatmen</t>
+    <t>glucocorticoiduse~n</t>
   </si>
   <si>
-    <t>clinicalstudydrugused</t>
+    <t>clinicalstudydrug~d</t>
   </si>
   <si>
     <t>bevacizumabused</t>
   </si>
   <si>
-    <t>threeormorechemotherapydrugs</t>
+    <t>threeormorechemot~s</t>
   </si>
   <si>
     <t>io_mono#c.pdl1</t>
   </si>
   <si>
-    <t>nonfirstlinechemotherapy#c.pdl1</t>
+    <t>nonfirstlinechemo~y#</t>
   </si>
   <si>
-    <t>firstlinecombinationtherapy#c.pdl1</t>
+    <t>c.pdl1</t>
   </si>
   <si>
-    <t>firstlinechemotherapy#c.pdl1</t>
+    <t>firstlinecombinat~y#</t>
+  </si>
+  <si>
+    <t>firstlinechemothe~y#</t>
   </si>
   <si>
     <t>antialkdrug#c.pdl1</t>
@@ -276,10 +279,10 @@
     <t>metinhibitor#c.pdl1</t>
   </si>
   <si>
-    <t>carboplatinmonotherapy#c.pdl1</t>
+    <t>carboplatinmonoth~y#</t>
   </si>
   <si>
-    <t>cisplatinmonotherapy#c.pdl1</t>
+    <t>cisplatinmonother~y#</t>
   </si>
   <si>
     <t>_cons</t>
@@ -289,7 +292,167 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="950">
+  <fonts count="990">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -4099,7 +4262,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="950">
+  <borders count="990">
     <border>
       <left/>
       <right/>
@@ -10703,6 +10866,286 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="thin"/>
@@ -10754,7 +11197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="950">
+  <cellXfs count="990">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -14549,6 +14992,166 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="949" fillId="0" borderId="949" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="950" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="951" fillId="0" borderId="951" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="952" fillId="0" borderId="952" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="953" fillId="0" borderId="953" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="0" borderId="954" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="955" fillId="0" borderId="955" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="0" borderId="956" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="957" fillId="0" borderId="957" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="0" borderId="958" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="959" fillId="0" borderId="959" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="960" fillId="0" borderId="960" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="961" fillId="0" borderId="961" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="962" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="963" fillId="0" borderId="963" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="964" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="965" fillId="0" borderId="965" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="966" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="967" fillId="0" borderId="967" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="968" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="969" fillId="0" borderId="969" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="970" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="971" fillId="0" borderId="971" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="972" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="973" fillId="0" borderId="973" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="974" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="975" fillId="0" borderId="975" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="976" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="977" fillId="0" borderId="977" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="978" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="979" fillId="0" borderId="979" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="980" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="981" fillId="0" borderId="981" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="982" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="983" fillId="0" borderId="983" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="984" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="985" fillId="0" borderId="985" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="986" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="987" fillId="0" borderId="987" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="988" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="989" fillId="0" borderId="989" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14561,7 +15164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16474,54 +17077,54 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="680">
-        <v>1</v>
-      </c>
-      <c r="B84" s="681">
-        <v>0.73402279999999998</v>
-      </c>
-      <c r="C84" s="682">
-        <v>0.47016669999999999</v>
-      </c>
-      <c r="D84" s="683">
-        <v>-0.47999999999999998</v>
-      </c>
-      <c r="E84" s="684">
-        <v>0.629</v>
-      </c>
-      <c r="F84" s="685">
-        <v>0.2091635</v>
-      </c>
-      <c r="G84" s="686">
-        <v>2.5759249999999998</v>
+      <c r="A84" s="680" t="s">
+        <v>79</v>
+      </c>
+      <c r="B84" s="681" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="682" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" s="683" t="s">
+        <v>6</v>
+      </c>
+      <c r="E84" s="684" t="s">
+        <v>6</v>
+      </c>
+      <c r="F84" s="685" t="s">
+        <v>6</v>
+      </c>
+      <c r="G84" s="686" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="688" t="s">
-        <v>6</v>
-      </c>
-      <c r="B85" s="689" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="690" t="s">
-        <v>6</v>
-      </c>
-      <c r="D85" s="691" t="s">
-        <v>6</v>
-      </c>
-      <c r="E85" s="692" t="s">
-        <v>6</v>
-      </c>
-      <c r="F85" s="693" t="s">
-        <v>6</v>
-      </c>
-      <c r="G85" s="694" t="s">
-        <v>6</v>
+      <c r="A85" s="688">
+        <v>1</v>
+      </c>
+      <c r="B85" s="689">
+        <v>0.73402279999999998</v>
+      </c>
+      <c r="C85" s="690">
+        <v>0.47016669999999999</v>
+      </c>
+      <c r="D85" s="691">
+        <v>-0.47999999999999998</v>
+      </c>
+      <c r="E85" s="692">
+        <v>0.629</v>
+      </c>
+      <c r="F85" s="693">
+        <v>0.2091635</v>
+      </c>
+      <c r="G85" s="694">
+        <v>2.5759249999999998</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="696" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="B86" s="697" t="s">
         <v>6</v>
@@ -16543,31 +17146,31 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="704">
-        <v>1</v>
-      </c>
-      <c r="B87" s="705">
-        <v>0.85340130000000003</v>
-      </c>
-      <c r="C87" s="706">
-        <v>0.23498920000000001</v>
-      </c>
-      <c r="D87" s="707">
-        <v>-0.57999999999999996</v>
-      </c>
-      <c r="E87" s="708">
-        <v>0.56499999999999995</v>
-      </c>
-      <c r="F87" s="709">
-        <v>0.49747340000000001</v>
-      </c>
-      <c r="G87" s="710">
-        <v>1.463986</v>
+      <c r="A87" s="704" t="s">
+        <v>80</v>
+      </c>
+      <c r="B87" s="705" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="706" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" s="707" t="s">
+        <v>6</v>
+      </c>
+      <c r="E87" s="708" t="s">
+        <v>6</v>
+      </c>
+      <c r="F87" s="709" t="s">
+        <v>6</v>
+      </c>
+      <c r="G87" s="710" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="712" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="B88" s="713" t="s">
         <v>6</v>
@@ -16589,54 +17192,54 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="720" t="s">
-        <v>80</v>
-      </c>
-      <c r="B89" s="721" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="722" t="s">
-        <v>6</v>
-      </c>
-      <c r="D89" s="723" t="s">
-        <v>6</v>
-      </c>
-      <c r="E89" s="724" t="s">
-        <v>6</v>
-      </c>
-      <c r="F89" s="725" t="s">
-        <v>6</v>
-      </c>
-      <c r="G89" s="726" t="s">
-        <v>6</v>
+      <c r="A89" s="720">
+        <v>1</v>
+      </c>
+      <c r="B89" s="721">
+        <v>0.85340130000000003</v>
+      </c>
+      <c r="C89" s="722">
+        <v>0.23498920000000001</v>
+      </c>
+      <c r="D89" s="723">
+        <v>-0.57999999999999996</v>
+      </c>
+      <c r="E89" s="724">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="F89" s="725">
+        <v>0.49747340000000001</v>
+      </c>
+      <c r="G89" s="726">
+        <v>1.463986</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="728">
-        <v>1</v>
-      </c>
-      <c r="B90" s="729">
-        <v>0.95371859999999997</v>
-      </c>
-      <c r="C90" s="730">
-        <v>0.2572778</v>
-      </c>
-      <c r="D90" s="731">
-        <v>-0.17999999999999999</v>
-      </c>
-      <c r="E90" s="732">
-        <v>0.86099999999999999</v>
-      </c>
-      <c r="F90" s="733">
-        <v>0.56207940000000001</v>
-      </c>
-      <c r="G90" s="734">
-        <v>1.618239</v>
+      <c r="A90" s="728" t="s">
+        <v>6</v>
+      </c>
+      <c r="B90" s="729" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="730" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" s="731" t="s">
+        <v>6</v>
+      </c>
+      <c r="E90" s="732" t="s">
+        <v>6</v>
+      </c>
+      <c r="F90" s="733" t="s">
+        <v>6</v>
+      </c>
+      <c r="G90" s="734" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="736" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="B91" s="737" t="s">
         <v>6</v>
@@ -16659,7 +17262,7 @@
     </row>
     <row r="92">
       <c r="A92" s="744" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B92" s="745" t="s">
         <v>6</v>
@@ -16685,22 +17288,22 @@
         <v>1</v>
       </c>
       <c r="B93" s="753">
-        <v>4.7450479999999997</v>
+        <v>0.95371859999999997</v>
       </c>
       <c r="C93" s="754">
-        <v>3.7689650000000001</v>
+        <v>0.2572778</v>
       </c>
       <c r="D93" s="755">
-        <v>1.96</v>
+        <v>-0.17999999999999999</v>
       </c>
       <c r="E93" s="756">
-        <v>0.050000000000000003</v>
+        <v>0.86099999999999999</v>
       </c>
       <c r="F93" s="757">
-        <v>1.000313</v>
+        <v>0.56207940000000001</v>
       </c>
       <c r="G93" s="758">
-        <v>22.508430000000001</v>
+        <v>1.618239</v>
       </c>
     </row>
     <row r="94">
@@ -16754,22 +17357,22 @@
         <v>1</v>
       </c>
       <c r="B96" s="777">
-        <v>3.916696</v>
+        <v>4.7450479999999997</v>
       </c>
       <c r="C96" s="778">
-        <v>1.402658</v>
+        <v>3.7689650000000001</v>
       </c>
       <c r="D96" s="779">
-        <v>3.8100000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="E96" s="780">
-        <v>0</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="F96" s="781">
-        <v>1.9412670000000001</v>
+        <v>1.000313</v>
       </c>
       <c r="G96" s="782">
-        <v>7.9023199999999996</v>
+        <v>22.508430000000001</v>
       </c>
     </row>
     <row r="97">
@@ -16823,22 +17426,22 @@
         <v>1</v>
       </c>
       <c r="B99" s="801">
-        <v>2.5527570000000002</v>
+        <v>3.916696</v>
       </c>
       <c r="C99" s="802">
-        <v>1.6803349999999999</v>
+        <v>1.402658</v>
       </c>
       <c r="D99" s="803">
-        <v>1.4199999999999999</v>
+        <v>3.8100000000000001</v>
       </c>
       <c r="E99" s="804">
-        <v>0.155</v>
+        <v>0</v>
       </c>
       <c r="F99" s="805">
-        <v>0.70260590000000001</v>
+        <v>1.9412670000000001</v>
       </c>
       <c r="G99" s="806">
-        <v>9.2748519999999992</v>
+        <v>7.9023199999999996</v>
       </c>
     </row>
     <row r="100">
@@ -16892,22 +17495,22 @@
         <v>1</v>
       </c>
       <c r="B102" s="825">
-        <v>2.1889219999999998</v>
+        <v>2.5527570000000002</v>
       </c>
       <c r="C102" s="826">
-        <v>2.1302490000000001</v>
+        <v>1.6803349999999999</v>
       </c>
       <c r="D102" s="827">
-        <v>0.80000000000000004</v>
+        <v>1.4199999999999999</v>
       </c>
       <c r="E102" s="828">
-        <v>0.42099999999999999</v>
+        <v>0.155</v>
       </c>
       <c r="F102" s="829">
-        <v>0.32497110000000001</v>
+        <v>0.70260590000000001</v>
       </c>
       <c r="G102" s="830">
-        <v>14.744009999999999</v>
+        <v>9.2748519999999992</v>
       </c>
     </row>
     <row r="103">
@@ -16961,22 +17564,22 @@
         <v>1</v>
       </c>
       <c r="B105" s="849">
-        <v>1.4e+32</v>
+        <v>2.1889219999999998</v>
       </c>
       <c r="C105" s="850">
-        <v>1.32e+38</v>
+        <v>2.1302490000000001</v>
       </c>
       <c r="D105" s="851">
-        <v>0</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="E105" s="852">
-        <v>1</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="F105" s="853">
-        <v>0</v>
-      </c>
-      <c r="G105" s="854" t="s">
-        <v>14</v>
+        <v>0.32497110000000001</v>
+      </c>
+      <c r="G105" s="854">
+        <v>14.744009999999999</v>
       </c>
     </row>
     <row r="106">
@@ -17030,16 +17633,16 @@
         <v>1</v>
       </c>
       <c r="B108" s="873">
-        <v>3.4900000000000003e+48</v>
+        <v>1.4e+32</v>
       </c>
       <c r="C108" s="874">
-        <v>1.4e+52</v>
+        <v>1.32e+38</v>
       </c>
       <c r="D108" s="875">
-        <v>0.029999999999999999</v>
+        <v>0</v>
       </c>
       <c r="E108" s="876">
-        <v>0.97799999999999998</v>
+        <v>1</v>
       </c>
       <c r="F108" s="877">
         <v>0</v>
@@ -17099,22 +17702,22 @@
         <v>1</v>
       </c>
       <c r="B111" s="897">
-        <v>1.0699999999999999e-05</v>
+        <v>3.4900000000000003e+48</v>
       </c>
       <c r="C111" s="898">
-        <v>0.00018230000000000001</v>
+        <v>1.4e+52</v>
       </c>
       <c r="D111" s="899">
-        <v>-0.67000000000000004</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="E111" s="900">
-        <v>0.502</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F111" s="901">
-        <v>3.2399999999999998e-20</v>
-      </c>
-      <c r="G111" s="902">
-        <v>3520000000</v>
+        <v>0</v>
+      </c>
+      <c r="G111" s="902" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="112">
@@ -17164,71 +17767,186 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="920">
-        <v>1</v>
-      </c>
-      <c r="B114" s="921">
-        <v>0.1871294</v>
-      </c>
-      <c r="C114" s="922">
-        <v>0.74113949999999995</v>
-      </c>
-      <c r="D114" s="923">
-        <v>-0.41999999999999999</v>
-      </c>
-      <c r="E114" s="924">
-        <v>0.67200000000000004</v>
-      </c>
-      <c r="F114" s="925">
-        <v>7.9599999999999997e-05</v>
-      </c>
-      <c r="G114" s="926">
-        <v>439.9339</v>
+      <c r="A114" s="920" t="s">
+        <v>79</v>
+      </c>
+      <c r="B114" s="921" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="922" t="s">
+        <v>6</v>
+      </c>
+      <c r="D114" s="923" t="s">
+        <v>6</v>
+      </c>
+      <c r="E114" s="924" t="s">
+        <v>6</v>
+      </c>
+      <c r="F114" s="925" t="s">
+        <v>6</v>
+      </c>
+      <c r="G114" s="926" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="928" t="s">
-        <v>6</v>
-      </c>
-      <c r="B115" s="929" t="s">
-        <v>6</v>
-      </c>
-      <c r="C115" s="930" t="s">
-        <v>6</v>
-      </c>
-      <c r="D115" s="931" t="s">
-        <v>6</v>
-      </c>
-      <c r="E115" s="932" t="s">
-        <v>6</v>
-      </c>
-      <c r="F115" s="933" t="s">
-        <v>6</v>
-      </c>
-      <c r="G115" s="934" t="s">
-        <v>6</v>
+      <c r="A115" s="928">
+        <v>1</v>
+      </c>
+      <c r="B115" s="929">
+        <v>1.0699999999999999e-05</v>
+      </c>
+      <c r="C115" s="930">
+        <v>0.00018230000000000001</v>
+      </c>
+      <c r="D115" s="931">
+        <v>-0.67000000000000004</v>
+      </c>
+      <c r="E115" s="932">
+        <v>0.502</v>
+      </c>
+      <c r="F115" s="933">
+        <v>3.2399999999999998e-20</v>
+      </c>
+      <c r="G115" s="934">
+        <v>3520000000</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="943" t="s">
+      <c r="A116" s="936" t="s">
+        <v>6</v>
+      </c>
+      <c r="B116" s="937" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="938" t="s">
+        <v>6</v>
+      </c>
+      <c r="D116" s="939" t="s">
+        <v>6</v>
+      </c>
+      <c r="E116" s="940" t="s">
+        <v>6</v>
+      </c>
+      <c r="F116" s="941" t="s">
+        <v>6</v>
+      </c>
+      <c r="G116" s="942" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="944" t="s">
         <v>89</v>
       </c>
-      <c r="B116" s="944">
+      <c r="B117" s="945" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" s="946" t="s">
+        <v>6</v>
+      </c>
+      <c r="D117" s="947" t="s">
+        <v>6</v>
+      </c>
+      <c r="E117" s="948" t="s">
+        <v>6</v>
+      </c>
+      <c r="F117" s="949" t="s">
+        <v>6</v>
+      </c>
+      <c r="G117" s="950" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="952" t="s">
+        <v>79</v>
+      </c>
+      <c r="B118" s="953" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="954" t="s">
+        <v>6</v>
+      </c>
+      <c r="D118" s="955" t="s">
+        <v>6</v>
+      </c>
+      <c r="E118" s="956" t="s">
+        <v>6</v>
+      </c>
+      <c r="F118" s="957" t="s">
+        <v>6</v>
+      </c>
+      <c r="G118" s="958" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="960">
+        <v>1</v>
+      </c>
+      <c r="B119" s="961">
+        <v>0.1871294</v>
+      </c>
+      <c r="C119" s="962">
+        <v>0.74113949999999995</v>
+      </c>
+      <c r="D119" s="963">
+        <v>-0.41999999999999999</v>
+      </c>
+      <c r="E119" s="964">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="F119" s="965">
+        <v>7.9599999999999997e-05</v>
+      </c>
+      <c r="G119" s="966">
+        <v>439.9339</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="968" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="969" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="970" t="s">
+        <v>6</v>
+      </c>
+      <c r="D120" s="971" t="s">
+        <v>6</v>
+      </c>
+      <c r="E120" s="972" t="s">
+        <v>6</v>
+      </c>
+      <c r="F120" s="973" t="s">
+        <v>6</v>
+      </c>
+      <c r="G120" s="974" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="983" t="s">
+        <v>90</v>
+      </c>
+      <c r="B121" s="984">
         <v>4.2551620000000003</v>
       </c>
-      <c r="C116" s="945">
+      <c r="C121" s="985">
         <v>3.2829320000000002</v>
       </c>
-      <c r="D116" s="946">
+      <c r="D121" s="986">
         <v>1.8799999999999999</v>
       </c>
-      <c r="E116" s="947">
+      <c r="E121" s="987">
         <v>0.060999999999999999</v>
       </c>
-      <c r="F116" s="948">
+      <c r="F121" s="988">
         <v>0.93799200000000005</v>
       </c>
-      <c r="G116" s="949">
+      <c r="G121" s="989">
         <v>19.303370000000001</v>
       </c>
     </row>

--- a/mortality_odds_only_pdl1.xlsx
+++ b/mortality_odds_only_pdl1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="356" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="321" uniqueCount="90">
   <si>
     <t>mortality_outcome</t>
   </si>
@@ -39,16 +39,16 @@
     <t>io_mono</t>
   </si>
   <si>
-    <t>firstlinechemothe~y</t>
+    <t>firstlinechemotherapy</t>
   </si>
   <si>
-    <t>nonfirstlinechemo~y</t>
+    <t>nonfirstlinechemotherapy</t>
   </si>
   <si>
-    <t>otherfirstlinethe~y</t>
+    <t>otherfirstlinetherapy</t>
   </si>
   <si>
-    <t>firstlinecombinat~y</t>
+    <t>firstlinecombinationtherapy</t>
   </si>
   <si>
     <t>antibrafdrug</t>
@@ -63,10 +63,10 @@
     <t>metinhibitor</t>
   </si>
   <si>
-    <t>carboplatinmonoth~y</t>
+    <t>carboplatinmonotherapy</t>
   </si>
   <si>
-    <t>cisplatinmonother~y</t>
+    <t>cisplatinmonotherapy</t>
   </si>
   <si>
     <t>antialkdrug#alk</t>
@@ -111,10 +111,10 @@
     <t>ecog4</t>
   </si>
   <si>
-    <t>squamouscellcarci~a</t>
+    <t>squamouscellcarcinoma</t>
   </si>
   <si>
-    <t>nonsquamouscellca~a</t>
+    <t>nonsquamouscellcarcinoma</t>
   </si>
   <si>
     <t>pdl1</t>
@@ -147,13 +147,13 @@
     <t>male</t>
   </si>
   <si>
-    <t>daysfromadvancedd~t</t>
+    <t>daysfromadvanceddiagnosistotreat</t>
   </si>
   <si>
-    <t>patientassistance~m</t>
+    <t>patientassistanceprogram</t>
   </si>
   <si>
-    <t>othergovernmental~e</t>
+    <t>othergovernmentalinsurance</t>
   </si>
   <si>
     <t>medicare</t>
@@ -165,7 +165,7 @@
     <t>medicaid</t>
   </si>
   <si>
-    <t>commercialhealthp~n</t>
+    <t>commercialhealthplan</t>
   </si>
   <si>
     <t>noinsurance</t>
@@ -195,7 +195,7 @@
     <t>neversmoker</t>
   </si>
   <si>
-    <t>academicmedicalce~r</t>
+    <t>academicmedicalcenter</t>
   </si>
   <si>
     <t>kidney_bool</t>
@@ -204,10 +204,10 @@
     <t>liver_bool</t>
   </si>
   <si>
-    <t>connective_tissue~l</t>
+    <t>connective_tissue_bool</t>
   </si>
   <si>
-    <t>interstitiallungd~e</t>
+    <t>interstitiallungdisease</t>
   </si>
   <si>
     <t>diabetes</t>
@@ -222,43 +222,40 @@
     <t>othercnsmetastases</t>
   </si>
   <si>
-    <t>digestivesystemme~s</t>
+    <t>digestivesystemmetastases</t>
   </si>
   <si>
     <t>adrenalmetastases</t>
   </si>
   <si>
-    <t>unspecifiedmetast~s</t>
+    <t>unspecifiedmetastases</t>
   </si>
   <si>
-    <t>antiinfectiveusep~t</t>
+    <t>antiinfectiveusepriortotreatment</t>
   </si>
   <si>
-    <t>glucocorticoiduse~n</t>
+    <t>glucocorticoidusepriortotreatmen</t>
   </si>
   <si>
-    <t>clinicalstudydrug~d</t>
+    <t>clinicalstudydrugused</t>
   </si>
   <si>
     <t>bevacizumabused</t>
   </si>
   <si>
-    <t>threeormorechemot~s</t>
+    <t>threeormorechemotherapydrugs</t>
   </si>
   <si>
     <t>io_mono#c.pdl1</t>
   </si>
   <si>
-    <t>nonfirstlinechemo~y#</t>
+    <t>nonfirstlinechemotherapy#c.pdl1</t>
   </si>
   <si>
-    <t>c.pdl1</t>
+    <t>firstlinecombinationtherapy#c.pdl1</t>
   </si>
   <si>
-    <t>firstlinecombinat~y#</t>
-  </si>
-  <si>
-    <t>firstlinechemothe~y#</t>
+    <t>firstlinechemotherapy#c.pdl1</t>
   </si>
   <si>
     <t>antialkdrug#c.pdl1</t>
@@ -279,10 +276,10 @@
     <t>metinhibitor#c.pdl1</t>
   </si>
   <si>
-    <t>carboplatinmonoth~y#</t>
+    <t>carboplatinmonotherapy#c.pdl1</t>
   </si>
   <si>
-    <t>cisplatinmonother~y#</t>
+    <t>cisplatinmonotherapy#c.pdl1</t>
   </si>
   <si>
     <t>_cons</t>
@@ -292,167 +289,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="990">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
+  <fonts count="950">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -4262,7 +4099,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="990">
+  <borders count="950">
     <border>
       <left/>
       <right/>
@@ -10866,286 +10703,6 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="thin"/>
@@ -11197,7 +10754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="990">
+  <cellXfs count="950">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -14992,166 +14549,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="949" fillId="0" borderId="949" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="950" fillId="0" borderId="950" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="951" fillId="0" borderId="951" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="952" fillId="0" borderId="952" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="953" fillId="0" borderId="953" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="954" fillId="0" borderId="954" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="955" fillId="0" borderId="955" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="956" fillId="0" borderId="956" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="957" fillId="0" borderId="957" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="958" fillId="0" borderId="958" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="959" fillId="0" borderId="959" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="960" fillId="0" borderId="960" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="961" fillId="0" borderId="961" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="962" fillId="0" borderId="962" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="963" fillId="0" borderId="963" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="964" fillId="0" borderId="964" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="965" fillId="0" borderId="965" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="966" fillId="0" borderId="966" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="967" fillId="0" borderId="967" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="968" fillId="0" borderId="968" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="969" fillId="0" borderId="969" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="970" fillId="0" borderId="970" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="971" fillId="0" borderId="971" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="972" fillId="0" borderId="972" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="973" fillId="0" borderId="973" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="974" fillId="0" borderId="974" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="975" fillId="0" borderId="975" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="976" fillId="0" borderId="976" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="977" fillId="0" borderId="977" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="978" fillId="0" borderId="978" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="979" fillId="0" borderId="979" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="980" fillId="0" borderId="980" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="981" fillId="0" borderId="981" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="982" fillId="0" borderId="982" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="983" fillId="0" borderId="983" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="984" fillId="0" borderId="984" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="985" fillId="0" borderId="985" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="986" fillId="0" borderId="986" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="987" fillId="0" borderId="987" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="988" fillId="0" borderId="988" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="989" fillId="0" borderId="989" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -15164,7 +14561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17077,54 +16474,54 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="680" t="s">
-        <v>79</v>
-      </c>
-      <c r="B84" s="681" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="682" t="s">
-        <v>6</v>
-      </c>
-      <c r="D84" s="683" t="s">
-        <v>6</v>
-      </c>
-      <c r="E84" s="684" t="s">
-        <v>6</v>
-      </c>
-      <c r="F84" s="685" t="s">
-        <v>6</v>
-      </c>
-      <c r="G84" s="686" t="s">
-        <v>6</v>
+      <c r="A84" s="680">
+        <v>1</v>
+      </c>
+      <c r="B84" s="681">
+        <v>0.73402279999999998</v>
+      </c>
+      <c r="C84" s="682">
+        <v>0.47016669999999999</v>
+      </c>
+      <c r="D84" s="683">
+        <v>-0.47999999999999998</v>
+      </c>
+      <c r="E84" s="684">
+        <v>0.629</v>
+      </c>
+      <c r="F84" s="685">
+        <v>0.2091635</v>
+      </c>
+      <c r="G84" s="686">
+        <v>2.5759249999999998</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="688">
-        <v>1</v>
-      </c>
-      <c r="B85" s="689">
-        <v>0.73402279999999998</v>
-      </c>
-      <c r="C85" s="690">
-        <v>0.47016669999999999</v>
-      </c>
-      <c r="D85" s="691">
-        <v>-0.47999999999999998</v>
-      </c>
-      <c r="E85" s="692">
-        <v>0.629</v>
-      </c>
-      <c r="F85" s="693">
-        <v>0.2091635</v>
-      </c>
-      <c r="G85" s="694">
-        <v>2.5759249999999998</v>
+      <c r="A85" s="688" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" s="689" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="690" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" s="691" t="s">
+        <v>6</v>
+      </c>
+      <c r="E85" s="692" t="s">
+        <v>6</v>
+      </c>
+      <c r="F85" s="693" t="s">
+        <v>6</v>
+      </c>
+      <c r="G85" s="694" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="696" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="B86" s="697" t="s">
         <v>6</v>
@@ -17146,31 +16543,31 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="704" t="s">
-        <v>80</v>
-      </c>
-      <c r="B87" s="705" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87" s="706" t="s">
-        <v>6</v>
-      </c>
-      <c r="D87" s="707" t="s">
-        <v>6</v>
-      </c>
-      <c r="E87" s="708" t="s">
-        <v>6</v>
-      </c>
-      <c r="F87" s="709" t="s">
-        <v>6</v>
-      </c>
-      <c r="G87" s="710" t="s">
-        <v>6</v>
+      <c r="A87" s="704">
+        <v>1</v>
+      </c>
+      <c r="B87" s="705">
+        <v>0.85340130000000003</v>
+      </c>
+      <c r="C87" s="706">
+        <v>0.23498920000000001</v>
+      </c>
+      <c r="D87" s="707">
+        <v>-0.57999999999999996</v>
+      </c>
+      <c r="E87" s="708">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="F87" s="709">
+        <v>0.49747340000000001</v>
+      </c>
+      <c r="G87" s="710">
+        <v>1.463986</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="712" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="B88" s="713" t="s">
         <v>6</v>
@@ -17192,54 +16589,54 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="720">
-        <v>1</v>
-      </c>
-      <c r="B89" s="721">
-        <v>0.85340130000000003</v>
-      </c>
-      <c r="C89" s="722">
-        <v>0.23498920000000001</v>
-      </c>
-      <c r="D89" s="723">
-        <v>-0.57999999999999996</v>
-      </c>
-      <c r="E89" s="724">
-        <v>0.56499999999999995</v>
-      </c>
-      <c r="F89" s="725">
-        <v>0.49747340000000001</v>
-      </c>
-      <c r="G89" s="726">
-        <v>1.463986</v>
+      <c r="A89" s="720" t="s">
+        <v>80</v>
+      </c>
+      <c r="B89" s="721" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="722" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" s="723" t="s">
+        <v>6</v>
+      </c>
+      <c r="E89" s="724" t="s">
+        <v>6</v>
+      </c>
+      <c r="F89" s="725" t="s">
+        <v>6</v>
+      </c>
+      <c r="G89" s="726" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="728" t="s">
-        <v>6</v>
-      </c>
-      <c r="B90" s="729" t="s">
-        <v>6</v>
-      </c>
-      <c r="C90" s="730" t="s">
-        <v>6</v>
-      </c>
-      <c r="D90" s="731" t="s">
-        <v>6</v>
-      </c>
-      <c r="E90" s="732" t="s">
-        <v>6</v>
-      </c>
-      <c r="F90" s="733" t="s">
-        <v>6</v>
-      </c>
-      <c r="G90" s="734" t="s">
-        <v>6</v>
+      <c r="A90" s="728">
+        <v>1</v>
+      </c>
+      <c r="B90" s="729">
+        <v>0.95371859999999997</v>
+      </c>
+      <c r="C90" s="730">
+        <v>0.2572778</v>
+      </c>
+      <c r="D90" s="731">
+        <v>-0.17999999999999999</v>
+      </c>
+      <c r="E90" s="732">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="F90" s="733">
+        <v>0.56207940000000001</v>
+      </c>
+      <c r="G90" s="734">
+        <v>1.618239</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="736" t="s">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="B91" s="737" t="s">
         <v>6</v>
@@ -17262,7 +16659,7 @@
     </row>
     <row r="92">
       <c r="A92" s="744" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B92" s="745" t="s">
         <v>6</v>
@@ -17288,22 +16685,22 @@
         <v>1</v>
       </c>
       <c r="B93" s="753">
-        <v>0.95371859999999997</v>
+        <v>4.7450479999999997</v>
       </c>
       <c r="C93" s="754">
-        <v>0.2572778</v>
+        <v>3.7689650000000001</v>
       </c>
       <c r="D93" s="755">
-        <v>-0.17999999999999999</v>
+        <v>1.96</v>
       </c>
       <c r="E93" s="756">
-        <v>0.86099999999999999</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="F93" s="757">
-        <v>0.56207940000000001</v>
+        <v>1.000313</v>
       </c>
       <c r="G93" s="758">
-        <v>1.618239</v>
+        <v>22.508430000000001</v>
       </c>
     </row>
     <row r="94">
@@ -17357,22 +16754,22 @@
         <v>1</v>
       </c>
       <c r="B96" s="777">
-        <v>4.7450479999999997</v>
+        <v>3.916696</v>
       </c>
       <c r="C96" s="778">
-        <v>3.7689650000000001</v>
+        <v>1.402658</v>
       </c>
       <c r="D96" s="779">
-        <v>1.96</v>
+        <v>3.8100000000000001</v>
       </c>
       <c r="E96" s="780">
-        <v>0.050000000000000003</v>
+        <v>0</v>
       </c>
       <c r="F96" s="781">
-        <v>1.000313</v>
+        <v>1.9412670000000001</v>
       </c>
       <c r="G96" s="782">
-        <v>22.508430000000001</v>
+        <v>7.9023199999999996</v>
       </c>
     </row>
     <row r="97">
@@ -17426,22 +16823,22 @@
         <v>1</v>
       </c>
       <c r="B99" s="801">
-        <v>3.916696</v>
+        <v>2.5527570000000002</v>
       </c>
       <c r="C99" s="802">
-        <v>1.402658</v>
+        <v>1.6803349999999999</v>
       </c>
       <c r="D99" s="803">
-        <v>3.8100000000000001</v>
+        <v>1.4199999999999999</v>
       </c>
       <c r="E99" s="804">
-        <v>0</v>
+        <v>0.155</v>
       </c>
       <c r="F99" s="805">
-        <v>1.9412670000000001</v>
+        <v>0.70260590000000001</v>
       </c>
       <c r="G99" s="806">
-        <v>7.9023199999999996</v>
+        <v>9.2748519999999992</v>
       </c>
     </row>
     <row r="100">
@@ -17495,22 +16892,22 @@
         <v>1</v>
       </c>
       <c r="B102" s="825">
-        <v>2.5527570000000002</v>
+        <v>2.1889219999999998</v>
       </c>
       <c r="C102" s="826">
-        <v>1.6803349999999999</v>
+        <v>2.1302490000000001</v>
       </c>
       <c r="D102" s="827">
-        <v>1.4199999999999999</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="E102" s="828">
-        <v>0.155</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="F102" s="829">
-        <v>0.70260590000000001</v>
+        <v>0.32497110000000001</v>
       </c>
       <c r="G102" s="830">
-        <v>9.2748519999999992</v>
+        <v>14.744009999999999</v>
       </c>
     </row>
     <row r="103">
@@ -17564,22 +16961,22 @@
         <v>1</v>
       </c>
       <c r="B105" s="849">
-        <v>2.1889219999999998</v>
+        <v>1.4e+32</v>
       </c>
       <c r="C105" s="850">
-        <v>2.1302490000000001</v>
+        <v>1.32e+38</v>
       </c>
       <c r="D105" s="851">
-        <v>0.80000000000000004</v>
+        <v>0</v>
       </c>
       <c r="E105" s="852">
-        <v>0.42099999999999999</v>
+        <v>1</v>
       </c>
       <c r="F105" s="853">
-        <v>0.32497110000000001</v>
-      </c>
-      <c r="G105" s="854">
-        <v>14.744009999999999</v>
+        <v>0</v>
+      </c>
+      <c r="G105" s="854" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="106">
@@ -17633,16 +17030,16 @@
         <v>1</v>
       </c>
       <c r="B108" s="873">
-        <v>1.4e+32</v>
+        <v>3.4900000000000003e+48</v>
       </c>
       <c r="C108" s="874">
-        <v>1.32e+38</v>
+        <v>1.4e+52</v>
       </c>
       <c r="D108" s="875">
-        <v>0</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="E108" s="876">
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F108" s="877">
         <v>0</v>
@@ -17702,22 +17099,22 @@
         <v>1</v>
       </c>
       <c r="B111" s="897">
-        <v>3.4900000000000003e+48</v>
+        <v>1.0699999999999999e-05</v>
       </c>
       <c r="C111" s="898">
-        <v>1.4e+52</v>
+        <v>0.00018230000000000001</v>
       </c>
       <c r="D111" s="899">
-        <v>0.029999999999999999</v>
+        <v>-0.67000000000000004</v>
       </c>
       <c r="E111" s="900">
-        <v>0.97799999999999998</v>
+        <v>0.502</v>
       </c>
       <c r="F111" s="901">
-        <v>0</v>
-      </c>
-      <c r="G111" s="902" t="s">
-        <v>14</v>
+        <v>3.2399999999999998e-20</v>
+      </c>
+      <c r="G111" s="902">
+        <v>3520000000</v>
       </c>
     </row>
     <row r="112">
@@ -17767,186 +17164,71 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="920" t="s">
-        <v>79</v>
-      </c>
-      <c r="B114" s="921" t="s">
-        <v>6</v>
-      </c>
-      <c r="C114" s="922" t="s">
-        <v>6</v>
-      </c>
-      <c r="D114" s="923" t="s">
-        <v>6</v>
-      </c>
-      <c r="E114" s="924" t="s">
-        <v>6</v>
-      </c>
-      <c r="F114" s="925" t="s">
-        <v>6</v>
-      </c>
-      <c r="G114" s="926" t="s">
-        <v>6</v>
+      <c r="A114" s="920">
+        <v>1</v>
+      </c>
+      <c r="B114" s="921">
+        <v>0.1871294</v>
+      </c>
+      <c r="C114" s="922">
+        <v>0.74113949999999995</v>
+      </c>
+      <c r="D114" s="923">
+        <v>-0.41999999999999999</v>
+      </c>
+      <c r="E114" s="924">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="F114" s="925">
+        <v>7.9599999999999997e-05</v>
+      </c>
+      <c r="G114" s="926">
+        <v>439.9339</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="928">
-        <v>1</v>
-      </c>
-      <c r="B115" s="929">
-        <v>1.0699999999999999e-05</v>
-      </c>
-      <c r="C115" s="930">
-        <v>0.00018230000000000001</v>
-      </c>
-      <c r="D115" s="931">
-        <v>-0.67000000000000004</v>
-      </c>
-      <c r="E115" s="932">
-        <v>0.502</v>
-      </c>
-      <c r="F115" s="933">
-        <v>3.2399999999999998e-20</v>
-      </c>
-      <c r="G115" s="934">
-        <v>3520000000</v>
+      <c r="A115" s="928" t="s">
+        <v>6</v>
+      </c>
+      <c r="B115" s="929" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="930" t="s">
+        <v>6</v>
+      </c>
+      <c r="D115" s="931" t="s">
+        <v>6</v>
+      </c>
+      <c r="E115" s="932" t="s">
+        <v>6</v>
+      </c>
+      <c r="F115" s="933" t="s">
+        <v>6</v>
+      </c>
+      <c r="G115" s="934" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="936" t="s">
-        <v>6</v>
-      </c>
-      <c r="B116" s="937" t="s">
-        <v>6</v>
-      </c>
-      <c r="C116" s="938" t="s">
-        <v>6</v>
-      </c>
-      <c r="D116" s="939" t="s">
-        <v>6</v>
-      </c>
-      <c r="E116" s="940" t="s">
-        <v>6</v>
-      </c>
-      <c r="F116" s="941" t="s">
-        <v>6</v>
-      </c>
-      <c r="G116" s="942" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="944" t="s">
+      <c r="A116" s="943" t="s">
         <v>89</v>
       </c>
-      <c r="B117" s="945" t="s">
-        <v>6</v>
-      </c>
-      <c r="C117" s="946" t="s">
-        <v>6</v>
-      </c>
-      <c r="D117" s="947" t="s">
-        <v>6</v>
-      </c>
-      <c r="E117" s="948" t="s">
-        <v>6</v>
-      </c>
-      <c r="F117" s="949" t="s">
-        <v>6</v>
-      </c>
-      <c r="G117" s="950" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="952" t="s">
-        <v>79</v>
-      </c>
-      <c r="B118" s="953" t="s">
-        <v>6</v>
-      </c>
-      <c r="C118" s="954" t="s">
-        <v>6</v>
-      </c>
-      <c r="D118" s="955" t="s">
-        <v>6</v>
-      </c>
-      <c r="E118" s="956" t="s">
-        <v>6</v>
-      </c>
-      <c r="F118" s="957" t="s">
-        <v>6</v>
-      </c>
-      <c r="G118" s="958" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="960">
-        <v>1</v>
-      </c>
-      <c r="B119" s="961">
-        <v>0.1871294</v>
-      </c>
-      <c r="C119" s="962">
-        <v>0.74113949999999995</v>
-      </c>
-      <c r="D119" s="963">
-        <v>-0.41999999999999999</v>
-      </c>
-      <c r="E119" s="964">
-        <v>0.67200000000000004</v>
-      </c>
-      <c r="F119" s="965">
-        <v>7.9599999999999997e-05</v>
-      </c>
-      <c r="G119" s="966">
-        <v>439.9339</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="968" t="s">
-        <v>6</v>
-      </c>
-      <c r="B120" s="969" t="s">
-        <v>6</v>
-      </c>
-      <c r="C120" s="970" t="s">
-        <v>6</v>
-      </c>
-      <c r="D120" s="971" t="s">
-        <v>6</v>
-      </c>
-      <c r="E120" s="972" t="s">
-        <v>6</v>
-      </c>
-      <c r="F120" s="973" t="s">
-        <v>6</v>
-      </c>
-      <c r="G120" s="974" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="983" t="s">
-        <v>90</v>
-      </c>
-      <c r="B121" s="984">
+      <c r="B116" s="944">
         <v>4.2551620000000003</v>
       </c>
-      <c r="C121" s="985">
+      <c r="C116" s="945">
         <v>3.2829320000000002</v>
       </c>
-      <c r="D121" s="986">
+      <c r="D116" s="946">
         <v>1.8799999999999999</v>
       </c>
-      <c r="E121" s="987">
+      <c r="E116" s="947">
         <v>0.060999999999999999</v>
       </c>
-      <c r="F121" s="988">
+      <c r="F116" s="948">
         <v>0.93799200000000005</v>
       </c>
-      <c r="G121" s="989">
+      <c r="G116" s="949">
         <v>19.303370000000001</v>
       </c>
     </row>
